--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -1654,6 +1654,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -3165,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B1179"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -3186,6 +3187,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="59" t="inlineStr">
         <is>
@@ -3200,6 +3202,37 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="59" t="inlineStr">
         <is>
@@ -3214,6 +3247,33 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
     <row r="66">
       <c r="B66" s="59" t="inlineStr">
         <is>
@@ -3228,6 +3288,36 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98">
       <c r="B98" s="59" t="inlineStr">
         <is>
@@ -3242,6 +3332,32 @@
         </is>
       </c>
     </row>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
     <row r="126">
       <c r="B126" s="59" t="inlineStr">
         <is>
@@ -3256,6 +3372,33 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
     <row r="155">
       <c r="B155" s="59" t="inlineStr">
         <is>
@@ -3270,6 +3413,63 @@
         </is>
       </c>
     </row>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
     <row r="214">
       <c r="B214" s="59" t="inlineStr">
         <is>
@@ -3284,6 +3484,33 @@
         </is>
       </c>
     </row>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
     <row r="243">
       <c r="B243" s="59" t="inlineStr">
         <is>
@@ -3298,6 +3525,38 @@
         </is>
       </c>
     </row>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
     <row r="277">
       <c r="B277" s="59" t="inlineStr">
         <is>
@@ -3312,6 +3571,38 @@
         </is>
       </c>
     </row>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
     <row r="311">
       <c r="B311" s="59" t="inlineStr">
         <is>
@@ -3326,6 +3617,43 @@
         </is>
       </c>
     </row>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
     <row r="350">
       <c r="B350" s="59" t="inlineStr">
         <is>
@@ -3340,6 +3668,32 @@
         </is>
       </c>
     </row>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
     <row r="378">
       <c r="B378" s="59" t="inlineStr">
         <is>
@@ -3354,6 +3708,32 @@
         </is>
       </c>
     </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
     <row r="406">
       <c r="B406" s="59" t="inlineStr">
         <is>
@@ -3368,6 +3748,32 @@
         </is>
       </c>
     </row>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
     <row r="434">
       <c r="B434" s="59" t="inlineStr">
         <is>
@@ -3382,6 +3788,85 @@
         </is>
       </c>
     </row>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
     <row r="515">
       <c r="B515" s="59" t="inlineStr">
         <is>
@@ -3396,6 +3881,32 @@
         </is>
       </c>
     </row>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
     <row r="543">
       <c r="B543" s="59" t="inlineStr">
         <is>
@@ -3410,6 +3921,32 @@
         </is>
       </c>
     </row>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
     <row r="571">
       <c r="B571" s="59" t="inlineStr">
         <is>
@@ -3424,6 +3961,46 @@
         </is>
       </c>
     </row>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
     <row r="613">
       <c r="B613" s="59" t="inlineStr">
         <is>
@@ -3438,6 +4015,32 @@
         </is>
       </c>
     </row>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
     <row r="641">
       <c r="B641" s="59" t="inlineStr">
         <is>
@@ -3452,6 +4055,32 @@
         </is>
       </c>
     </row>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
     <row r="669">
       <c r="B669" s="59" t="inlineStr">
         <is>
@@ -3466,6 +4095,32 @@
         </is>
       </c>
     </row>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
     <row r="697">
       <c r="B697" s="59" t="inlineStr">
         <is>
@@ -3480,6 +4135,91 @@
         </is>
       </c>
     </row>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
     <row r="784">
       <c r="B784" s="59" t="inlineStr">
         <is>
@@ -3494,6 +4234,69 @@
         </is>
       </c>
     </row>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
     <row r="849">
       <c r="B849" s="59" t="inlineStr">
         <is>
@@ -3508,6 +4311,32 @@
         </is>
       </c>
     </row>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
     <row r="877">
       <c r="B877" s="59" t="inlineStr">
         <is>
@@ -3522,6 +4351,36 @@
         </is>
       </c>
     </row>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
     <row r="909">
       <c r="B909" s="59" t="inlineStr">
         <is>
@@ -3536,6 +4395,32 @@
         </is>
       </c>
     </row>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
     <row r="937">
       <c r="B937" s="59" t="inlineStr">
         <is>
@@ -3550,6 +4435,32 @@
         </is>
       </c>
     </row>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
     <row r="965">
       <c r="B965" s="59" t="inlineStr">
         <is>
@@ -3564,6 +4475,32 @@
         </is>
       </c>
     </row>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
     <row r="993">
       <c r="B993" s="59" t="inlineStr">
         <is>
@@ -3578,6 +4515,32 @@
         </is>
       </c>
     </row>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
     <row r="1021">
       <c r="B1021" s="59" t="inlineStr">
         <is>
@@ -3592,6 +4555,32 @@
         </is>
       </c>
     </row>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
     <row r="1049">
       <c r="B1049" s="59" t="inlineStr">
         <is>
@@ -3606,6 +4595,49 @@
         </is>
       </c>
     </row>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
     <row r="1094">
       <c r="B1094" s="59" t="inlineStr">
         <is>
@@ -3620,6 +4652,32 @@
         </is>
       </c>
     </row>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
     <row r="1122">
       <c r="B1122" s="59" t="inlineStr">
         <is>
@@ -3634,6 +4692,32 @@
         </is>
       </c>
     </row>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
     <row r="1150">
       <c r="B1150" s="59" t="inlineStr">
         <is>
@@ -3648,6 +4732,32 @@
         </is>
       </c>
     </row>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
     <row r="1178">
       <c r="B1178" s="59" t="inlineStr">
         <is>
@@ -3702,6 +4812,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -3891,7 +5002,7 @@
       </c>
       <c r="C9" s="50" t="inlineStr">
         <is>
-          <t>Big Five (DNS de bigfive.ci)</t>
+          <t>Big Five (DNS de bigfive.solutions, chez Cloudflare)</t>
         </is>
       </c>
       <c r="D9" s="50" t="inlineStr">
@@ -3911,7 +5022,7 @@
       </c>
       <c r="G9" s="50" t="inlineStr">
         <is>
-          <t>Pointer emasterclass.bigfive.ci vers Vercel ; le développement pose la variable et redéploie.</t>
+          <t>Ajouter le domaine dans Vercel, puis le CNAME emasterclass dans Cloudflare, en « DNS only » ; le développement pose la variable et redéploie.</t>
         </is>
       </c>
       <c r="H9" s="51" t="inlineStr">
@@ -4301,6 +5412,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
         <is>
@@ -4791,6 +5904,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -13581,7 +14695,7 @@
       </c>
       <c r="E148" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.ci pointé, HTTPS actif, variables d'environnement de production posées</t>
+          <t>emasterclass.bigfive.solutions pointé, HTTPS actif, variables d'environnement de production posées</t>
         </is>
       </c>
       <c r="F148" s="33" t="inlineStr">
@@ -13618,7 +14732,7 @@
       </c>
       <c r="N148" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.ci n'est pas branché ; NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel.</t>
+          <t>emasterclass.bigfive.solutions n'est pas branché ; NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel.</t>
         </is>
       </c>
       <c r="O148" s="53" t="inlineStr">
@@ -14692,6 +15806,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -15698,7 +16813,7 @@
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.ci n'est pas encore branché ; NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel</t>
+          <t>emasterclass.bigfive.solutions n'est pas encore branché ; NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -17194,6 +18309,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -17463,7 +18579,7 @@
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>À déclarer dans la console FeexPay : https://emasterclass.bigfive.ci/api/paiements/feexpay/webhook?cle=&lt;FEEXPAY_WEBHOOK_CLE&gt; (ou en-tête Authorization: Bearer &lt;clé&gt;)</t>
+          <t>À déclarer dans la console FeexPay : https://emasterclass.bigfive.solutions/api/paiements/feexpay/webhook?cle=&lt;FEEXPAY_WEBHOOK_CLE&gt; (ou en-tête Authorization: Bearer &lt;clé&gt;)</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
@@ -19054,6 +20170,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -19109,7 +20226,7 @@
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.ci pointé sur Vercel, certificat actif. Zoom exige un contexte sécurisé pour la caméra et le micro.</t>
+          <t>emasterclass.bigfive.solutions pointé sur Vercel, certificat actif. Zoom exige un contexte sécurisé pour la caméra et le micro.</t>
         </is>
       </c>
       <c r="E5" s="33" t="inlineStr">
@@ -19142,7 +20259,7 @@
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
-          <t>NUXT_PUBLIC_SITE_URL=https://emasterclass.bigfive.ci (sitemap, canonical, QR des attestations).</t>
+          <t>NUXT_PUBLIC_SITE_URL=https://emasterclass.bigfive.solutions (sitemap, canonical, QR des attestations).</t>
         </is>
       </c>
       <c r="E6" s="33" t="inlineStr">
@@ -19439,7 +20556,7 @@
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>Déclarer https://emasterclass.bigfive.ci/api/paiements/feexpay/webhook?cle=&lt;FEEXPAY_WEBHOOK_CLE&gt; (ou en-tête Authorization: Bearer &lt;clé&gt;). Aucune URL de redirection : le paiement se fait dans un widget, sans quitter la page.</t>
+          <t>Déclarer https://emasterclass.bigfive.solutions/api/paiements/feexpay/webhook?cle=&lt;FEEXPAY_WEBHOOK_CLE&gt; (ou en-tête Authorization: Bearer &lt;clé&gt;). Aucune URL de redirection : le paiement se fait dans un widget, sans quitter la page.</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
@@ -20023,6 +21140,7 @@
       </c>
       <c r="G32" s="33" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="45" customHeight="1" s="31">
       <c r="A34" s="43" t="inlineStr">
         <is>
@@ -20030,6 +21148,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="58" t="inlineStr">
         <is>
@@ -20279,6 +21398,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -20368,7 +21488,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Compte Brevo, Resend, Postmark ou SMTP de l'hébergeur + SPF, DKIM, DMARC sur bigfive.ci</t>
+          <t>Compte Brevo, Resend, Postmark ou SMTP de l'hébergeur + SPF, DKIM, DMARC sur bigfiveabidjan.com</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
@@ -20530,7 +21650,7 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.ci pointé, certificat HTTPS, variables d'environnement posées</t>
+          <t>emasterclass.bigfive.solutions pointé, certificat HTTPS, variables d'environnement posées</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
@@ -21594,6 +22714,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -23234,6 +24355,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -23469,6 +24591,7 @@
       </c>
       <c r="E12" s="33" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="31.5" customHeight="1" s="31">
       <c r="A14" s="4" t="inlineStr">
         <is>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -531,6 +531,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -556,6 +559,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -567,7 +573,7 @@
       <row>67</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="5267325"/>
+    <ext cx="7239000" cy="4600575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -581,6 +587,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -589,10 +598,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="5267325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,6 +615,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -614,10 +626,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>128</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4629150"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -631,6 +643,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -642,7 +657,7 @@
       <row>156</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="10353675"/>
+    <ext cx="7239000" cy="4629150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -656,6 +671,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -664,10 +682,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>215</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4600575"/>
+    <ext cx="7239000" cy="10353675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -681,6 +699,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -692,7 +713,7 @@
       <row>244</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="5610225"/>
+    <ext cx="7239000" cy="4600575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -706,6 +727,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -714,10 +738,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>278</row>
+      <row>273</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="5591175"/>
+    <ext cx="7239000" cy="5610225"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -731,6 +755,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -739,10 +766,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>312</row>
+      <row>307</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="6496050"/>
+    <ext cx="7239000" cy="5591175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -756,6 +783,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -764,10 +794,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>351</row>
+      <row>341</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="6334125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -781,6 +811,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -792,7 +825,7 @@
       <row>379</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="5934075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -806,6 +839,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -814,10 +850,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>407</row>
+      <row>415</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="6334125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -831,6 +867,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -839,10 +878,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>435</row>
+      <row>453</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="14601825"/>
+    <ext cx="7239000" cy="6496050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -856,6 +895,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -864,7 +906,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>516</row>
+      <row>492</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -881,6 +923,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -889,7 +934,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>544</row>
+      <row>520</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -906,6 +951,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -914,10 +962,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>572</row>
+      <row>548</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="7115175"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -931,6 +979,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -939,10 +990,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>614</row>
+      <row>576</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="14601825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -956,6 +1007,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -964,7 +1018,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>642</row>
+      <row>657</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -981,6 +1035,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -989,7 +1046,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>670</row>
+      <row>685</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1006,6 +1063,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1014,10 +1074,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>698</row>
+      <row>713</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="15668625"/>
+    <ext cx="7239000" cy="7115175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -1031,6 +1091,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1039,10 +1102,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>785</row>
+      <row>755</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="11601450"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -1056,6 +1119,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1064,7 +1130,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>850</row>
+      <row>783</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1081,6 +1147,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1089,10 +1158,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>878</row>
+      <row>811</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="5267325"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -1106,6 +1175,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1114,10 +1186,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>910</row>
+      <row>839</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="15668625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -1131,6 +1203,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1139,10 +1214,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>938</row>
+      <row>926</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="11601450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -1156,6 +1231,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1164,7 +1242,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>966</row>
+      <row>991</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1181,6 +1259,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1189,10 +1270,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>994</row>
+      <row>1019</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="5267325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -1206,6 +1287,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1214,7 +1298,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1022</row>
+      <row>1051</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1231,6 +1315,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1239,10 +1326,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1050</row>
+      <row>1079</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="7724775"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -1256,6 +1343,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1264,7 +1354,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1095</row>
+      <row>1107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1281,6 +1371,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1289,7 +1382,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1123</row>
+      <row>1135</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1306,6 +1399,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1314,7 +1410,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1151</row>
+      <row>1163</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1331,6 +1427,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1339,10 +1438,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1179</row>
+      <row>1191</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="7724775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1356,6 +1455,177 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1236</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1264</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1292</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1320</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1348</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11430000" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1376</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11430000" cy="7877175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1654,7 +1924,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -2024,7 +2293,7 @@
     <row r="39" ht="27.75" customHeight="1" s="31">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>• FeexPay — Mobile Money et Wave en live. Carte (Visa, Djamo) refusée par FeexPay : KYC carte de la boutique en brouillon (403 CARD_PAYMENT_NOT_AUTHORIZED, 15/10) — action Big Five. Voir « En attente client », C1.</t>
+          <t>• FeexPay — Orange, MTN et Moov ouverts en live, webhook opérationnel (paiement MTN réel du 15/10 refusé par MTN pour solde ou plafond, et tracé). Wave : Clé agrégée Wave à activer (C14). Carte : KYC carte en brouillon (C1) — actions Big Five.</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2314,7 @@
     <row r="42" ht="27.75" customHeight="1" s="31">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>• Zoom — Meeting SDK intégré, en simulation : l'app Zoom Server-to-Server est désactivée et le Client ID du Meeting SDK manque (15/10) — action Big Five. Voir « En attente client », C2.</t>
+          <t>• Zoom — réglé le 15/10 (app activée, clés posées, mode live) ; reste le test réel de bout en bout (Z6 à Z9).</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2328,14 @@
     <row r="44" ht="27.75" customHeight="1" s="31">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>• Mot de passe de démonstration commun encore actif sur tous les comptes et écrit dans le README.</t>
+          <t>• Mot de passe de démonstration commun encore actif sur 6 comptes sur 7 ; retiré du README le 15/10, script de renouvellement prêt (D2).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="27.75" customHeight="1" s="31">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>• Domaine de production : NUXT_PUBLIC_SITE_URL pointe encore vers l'URL Vercel (sitemap, canonical, QR des attestations).</t>
+          <t>• Domaine de production : https://emasterclass.bigfive.solutions/ est l'URL définitive, branchée et en HTTPS depuis le 15/10.</t>
         </is>
       </c>
     </row>
@@ -2080,14 +2349,14 @@
     <row r="47" ht="27.75" customHeight="1" s="31">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>• /admin/apprenants plante (erreur 500) depuis le 15/10 : création et export d'apprenants indisponibles — reste dev (D1).</t>
+          <t>• /admin/apprenants : l'erreur 500 du 15/10 est corrigée (27d835b) et vérifiée ; reste à rejouer la création d'un apprenant (ADM-12).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="27.75" customHeight="1" s="31">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié — à changer immédiatement (D2).</t>
+          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration : lancer npm run auth:renouveler -- --appliquer (D2).</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="B1:B1376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -3187,7 +3456,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="59" t="inlineStr">
         <is>
@@ -3202,37 +3470,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="59" t="inlineStr">
         <is>
@@ -3243,1532 +3480,532 @@
     <row r="38">
       <c r="B38" s="60" t="inlineStr">
         <is>
-          <t>Cas : VIT-17, ACH-10, ATT-09, SEC-07, SEO-10, EXP-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
+          <t>Cas : SEO-10</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
       <c r="B66" s="59" t="inlineStr">
         <is>
-          <t>BLQ-GA4 — ADM-17 : Bloqué — client · ADM-18 : Bloqué — client · SEO-11 : Bloqué — client</t>
+          <t>BLQ-FEEXPAY — Compte FeexPay au 15/10 : Mobile Money ouvert, Wave non activé, carte bloquée, webhook opérationnel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="60" t="inlineStr">
         <is>
+          <t>Cas : ACH-05, ACH-07, ACH-06, ACH-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="59" t="inlineStr">
+        <is>
+          <t>BLQ-GA4 — ADM-17 : Bloqué — client · ADM-18 : Bloqué — client · SEO-11 : Bloqué — client</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="60" t="inlineStr">
+        <is>
           <t>Cas : ADM-17, ADM-18, SEO-11</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98">
-      <c r="B98" s="59" t="inlineStr">
+    <row r="127">
+      <c r="B127" s="59" t="inlineStr">
         <is>
           <t>BLQ-JURIDIQUE — VIT-20 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="60" t="inlineStr">
+    <row r="128">
+      <c r="B128" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-20</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126">
-      <c r="B126" s="59" t="inlineStr">
-        <is>
-          <t>BLQ-KYC — FeexPay refuse le paiement par carte : KYC carte en brouillon (réponse API du 15/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="60" t="inlineStr">
-        <is>
-          <t>Cas : ACH-04, ACH-05, ACH-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
     <row r="155">
       <c r="B155" s="59" t="inlineStr">
         <is>
-          <t>BLQ-VIDEOS — VID-07 : Bloqué — client</t>
+          <t>BLQ-KYC — FeexPay refuse le paiement par carte : KYC carte en brouillon (réponse API du 15/10)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="60" t="inlineStr">
         <is>
+          <t>Cas : ACH-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="59" t="inlineStr">
+        <is>
+          <t>BLQ-VIDEOS — VID-07 : Bloqué — client</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="60" t="inlineStr">
+        <is>
           <t>Cas : VID-07</t>
         </is>
       </c>
     </row>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214">
-      <c r="B214" s="59" t="inlineStr">
-        <is>
-          <t>BLQ-ZOOM — Zoom : app Server-to-Server désactivée, Client ID du Meeting SDK manquant</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="B215" s="60" t="inlineStr">
-        <is>
-          <t>Cas : COL-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
     <row r="243">
       <c r="B243" s="59" t="inlineStr">
         <is>
+          <t>BLQ-ZOOM — Zoom : app Server-to-Server désactivée, Client ID du Meeting SDK manquant</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="59" t="inlineStr">
+        <is>
           <t>ACH-03 — ACH-03 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="B244" s="60" t="inlineStr">
+    <row r="273">
+      <c r="B273" s="60" t="inlineStr">
         <is>
           <t>Cas : ACH-03</t>
         </is>
       </c>
     </row>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277">
-      <c r="B277" s="59" t="inlineStr">
+    <row r="306">
+      <c r="B306" s="59" t="inlineStr">
         <is>
           <t>ACH-04 — ACH-04 : OK</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="B278" s="60" t="inlineStr">
+    <row r="307">
+      <c r="B307" s="60" t="inlineStr">
         <is>
           <t>Cas : ACH-04</t>
         </is>
       </c>
     </row>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311">
-      <c r="B311" s="59" t="inlineStr">
-        <is>
-          <t>ACH-12 — ACH-12 : OK · ADM-26 : OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="B312" s="60" t="inlineStr">
-        <is>
-          <t>Cas : ACH-12, ADM-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350">
-      <c r="B350" s="59" t="inlineStr">
-        <is>
-          <t>ADM-05 — ADM-05 : OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="B351" s="60" t="inlineStr">
-        <is>
-          <t>Cas : ADM-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
+    <row r="340">
+      <c r="B340" s="59" t="inlineStr">
+        <is>
+          <t>ACH-04-carte — Carte (Visa, Djamo) affichée « Bientôt disponible », avec la raison</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="60" t="inlineStr">
+        <is>
+          <t>Cas : ACH-04</t>
+        </is>
+      </c>
+    </row>
     <row r="378">
       <c r="B378" s="59" t="inlineStr">
         <is>
-          <t>ADM-06 — ADM-06 : OK · ADM-07 : À retester</t>
+          <t>ACH-04-prefill — Fenêtre FeexPay pré-remplie : nom, e-mail, opérateur MTN déduit du 05, numéro</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="B379" s="60" t="inlineStr">
         <is>
+          <t>Cas : ACH-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="59" t="inlineStr">
+        <is>
+          <t>ACH-04-wave — Wave affiché « Bientôt disponible », avec la raison et le renvoi vers le Mobile Money</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="60" t="inlineStr">
+        <is>
+          <t>Cas : ACH-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" s="59" t="inlineStr">
+        <is>
+          <t>ACH-12 — ACH-12 : OK · ADM-26 : OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="60" t="inlineStr">
+        <is>
+          <t>Cas : ACH-12, ADM-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="59" t="inlineStr">
+        <is>
+          <t>ADM-05 — ADM-05 : OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="60" t="inlineStr">
+        <is>
+          <t>Cas : ADM-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="59" t="inlineStr">
+        <is>
+          <t>ADM-06 — ADM-06 : OK · ADM-07 : À retester</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="60" t="inlineStr">
+        <is>
           <t>Cas : ADM-06, ADM-07</t>
         </is>
       </c>
     </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406">
-      <c r="B406" s="59" t="inlineStr">
+    <row r="547" s="31">
+      <c r="B547" s="59" t="inlineStr">
         <is>
           <t>ADM-12 — /admin/apprenants : erreur 500 constatée le 15/10 (reste dev)</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="B407" s="60" t="inlineStr">
+    <row r="548" s="31">
+      <c r="B548" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-12, ADM-14</t>
         </is>
       </c>
     </row>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434">
-      <c r="B434" s="59" t="inlineStr">
+    <row r="575">
+      <c r="B575" s="59" t="inlineStr">
         <is>
           <t>ADM-20 — Transactions (admin supérieur) : les essais Visa / Djamo restent « En attente »</t>
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="B435" s="60" t="inlineStr">
+    <row r="576">
+      <c r="B576" s="60" t="inlineStr">
         <is>
           <t>Cas : ACH-05, ADM-20</t>
         </is>
       </c>
     </row>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515">
-      <c r="B515" s="59" t="inlineStr">
+    <row r="656">
+      <c r="B656" s="59" t="inlineStr">
         <is>
           <t>ADM-20-editeur — ADM-20 : OK</t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="B516" s="60" t="inlineStr">
+    <row r="657">
+      <c r="B657" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-20</t>
         </is>
       </c>
     </row>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543">
-      <c r="B543" s="59" t="inlineStr">
+    <row r="684">
+      <c r="B684" s="59" t="inlineStr">
         <is>
           <t>ADM-21 — ADM-21 : OK</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="B544" s="60" t="inlineStr">
+    <row r="685">
+      <c r="B685" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-21</t>
         </is>
       </c>
     </row>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571">
-      <c r="B571" s="59" t="inlineStr">
+    <row r="712">
+      <c r="B712" s="59" t="inlineStr">
         <is>
           <t>ADM-22 — ADM-22 : OK · ADM-23 : OK · ADM-24 : OK</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="B572" s="60" t="inlineStr">
+    <row r="713">
+      <c r="B713" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-22, ADM-23, ADM-24</t>
         </is>
       </c>
     </row>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613">
-      <c r="B613" s="59" t="inlineStr">
+    <row r="754">
+      <c r="B754" s="59" t="inlineStr">
         <is>
           <t>APP-03 — APP-03 : OK</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="B614" s="60" t="inlineStr">
+    <row r="755">
+      <c r="B755" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-03</t>
         </is>
       </c>
     </row>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641">
-      <c r="B641" s="59" t="inlineStr">
+    <row r="782">
+      <c r="B782" s="59" t="inlineStr">
         <is>
           <t>APP-05 — APP-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="B642" s="60" t="inlineStr">
+    <row r="783">
+      <c r="B783" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-05</t>
         </is>
       </c>
     </row>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669">
-      <c r="B669" s="59" t="inlineStr">
+    <row r="810">
+      <c r="B810" s="59" t="inlineStr">
         <is>
           <t>APP-07 — APP-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="B670" s="60" t="inlineStr">
+    <row r="811">
+      <c r="B811" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-07</t>
         </is>
       </c>
     </row>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697">
-      <c r="B697" s="59" t="inlineStr">
+    <row r="838">
+      <c r="B838" s="59" t="inlineStr">
         <is>
           <t>APP-07-mobile — APP-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="B698" s="60" t="inlineStr">
+    <row r="839">
+      <c r="B839" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-07</t>
         </is>
       </c>
     </row>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784">
-      <c r="B784" s="59" t="inlineStr">
+    <row r="925">
+      <c r="B925" s="59" t="inlineStr">
         <is>
           <t>ATT-05 — ATT-05 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="B785" s="60" t="inlineStr">
+    <row r="926">
+      <c r="B926" s="60" t="inlineStr">
         <is>
           <t>Cas : ATT-05</t>
         </is>
       </c>
     </row>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849">
-      <c r="B849" s="59" t="inlineStr">
+    <row r="990">
+      <c r="B990" s="59" t="inlineStr">
         <is>
           <t>ATT-07 — ATT-06 : OK · ATT-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="850">
-      <c r="B850" s="60" t="inlineStr">
+    <row r="991">
+      <c r="B991" s="60" t="inlineStr">
         <is>
           <t>Cas : ATT-06, ATT-07</t>
         </is>
       </c>
     </row>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877">
-      <c r="B877" s="59" t="inlineStr">
-        <is>
-          <t>COL-01 — COL-01 : OK · COL-06 : Bloqué — prestataire</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="B878" s="60" t="inlineStr">
+    <row r="1018">
+      <c r="B1018" s="59" t="inlineStr">
+        <is>
+          <t>COL-01 — COL-01 : OK · COL-06 : OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="B1019" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-01, COL-06</t>
         </is>
       </c>
     </row>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909">
-      <c r="B909" s="59" t="inlineStr">
+    <row r="1050">
+      <c r="B1050" s="59" t="inlineStr">
         <is>
           <t>COL-03 — COL-03 : À retester</t>
         </is>
       </c>
     </row>
-    <row r="910">
-      <c r="B910" s="60" t="inlineStr">
+    <row r="1051">
+      <c r="B1051" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-03</t>
         </is>
       </c>
     </row>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937">
-      <c r="B937" s="59" t="inlineStr">
+    <row r="1078">
+      <c r="B1078" s="59" t="inlineStr">
         <is>
           <t>COL-05-seance-passee — Séance du 19/09 affichée « EN DIRECT · 621 h » (reste dev)</t>
         </is>
       </c>
     </row>
-    <row r="938">
-      <c r="B938" s="60" t="inlineStr">
+    <row r="1079">
+      <c r="B1079" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-05</t>
         </is>
       </c>
     </row>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965">
-      <c r="B965" s="59" t="inlineStr">
+    <row r="1106">
+      <c r="B1106" s="59" t="inlineStr">
         <is>
           <t>FOR-05 — FOR-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="966">
-      <c r="B966" s="60" t="inlineStr">
+    <row r="1107">
+      <c r="B1107" s="60" t="inlineStr">
         <is>
           <t>Cas : FOR-05</t>
         </is>
       </c>
     </row>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993">
-      <c r="B993" s="59" t="inlineStr">
+    <row r="1134">
+      <c r="B1134" s="59" t="inlineStr">
         <is>
           <t>FOR-05-releve — FOR-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="994">
-      <c r="B994" s="60" t="inlineStr">
+    <row r="1135">
+      <c r="B1135" s="60" t="inlineStr">
         <is>
           <t>Cas : FOR-05</t>
         </is>
       </c>
     </row>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021">
-      <c r="B1021" s="59" t="inlineStr">
+    <row r="1162">
+      <c r="B1162" s="59" t="inlineStr">
         <is>
           <t>PRI-02 — PRI-02 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1022">
-      <c r="B1022" s="60" t="inlineStr">
+    <row r="1163">
+      <c r="B1163" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-02</t>
         </is>
       </c>
     </row>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049">
-      <c r="B1049" s="59" t="inlineStr">
+    <row r="1190">
+      <c r="B1190" s="59" t="inlineStr">
         <is>
           <t>PRI-02-admin — PRI-02 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1050">
-      <c r="B1050" s="60" t="inlineStr">
+    <row r="1191">
+      <c r="B1191" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-02</t>
         </is>
       </c>
     </row>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094">
-      <c r="B1094" s="59" t="inlineStr">
+    <row r="1235">
+      <c r="B1235" s="59" t="inlineStr">
         <is>
           <t>PRI-04 — PRI-04 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1095">
-      <c r="B1095" s="60" t="inlineStr">
+    <row r="1236">
+      <c r="B1236" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-04</t>
         </is>
       </c>
     </row>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122">
-      <c r="B1122" s="59" t="inlineStr">
+    <row r="1263">
+      <c r="B1263" s="59" t="inlineStr">
         <is>
           <t>VIT-11-accueil — VIT-11 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1123">
-      <c r="B1123" s="60" t="inlineStr">
+    <row r="1264">
+      <c r="B1264" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-11</t>
         </is>
       </c>
     </row>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150">
-      <c r="B1150" s="59" t="inlineStr">
+    <row r="1291">
+      <c r="B1291" s="59" t="inlineStr">
         <is>
           <t>VIT-12-fiche — VIT-12 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1151">
-      <c r="B1151" s="60" t="inlineStr">
+    <row r="1292">
+      <c r="B1292" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-12</t>
         </is>
       </c>
     </row>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
-    <row r="1164"/>
-    <row r="1165"/>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178">
-      <c r="B1178" s="59" t="inlineStr">
+    <row r="1319">
+      <c r="B1319" s="59" t="inlineStr">
         <is>
           <t>VIT-15 — VIT-15 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="1179">
-      <c r="B1179" s="60" t="inlineStr">
+    <row r="1320">
+      <c r="B1320" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="B1347" s="59" t="inlineStr">
+        <is>
+          <t>ADM-12-corrige — /admin/apprenants s'affiche de nouveau (corrigé le 15/10, 27d835b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="B1348" s="60" t="inlineStr">
+        <is>
+          <t>Cas : ADM-12, ADM-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="B1375" s="59" t="inlineStr">
+        <is>
+          <t>COL-05-corrige — Séance du 19/09 affichée « TERMINÉE · 19 septembre à 20:00 » (corrigé le 15/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="B1376" s="60" t="inlineStr">
+        <is>
+          <t>Cas : COL-05</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="31" min="1" max="1"/>
@@ -4812,7 +4049,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -4900,8 +4136,8 @@
       </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
-          <t>BLQ-KYC → Captures, ligne 126
-ADM-20 → Captures, ligne 434</t>
+          <t>BLQ-KYC → Captures, ligne 155
+ADM-20 → Captures, ligne 575</t>
         </is>
       </c>
     </row>
@@ -4913,12 +4149,12 @@
       </c>
       <c r="B7" s="49" t="inlineStr">
         <is>
-          <t>Zoom : application désactivée, identifiants du Meeting SDK incomplets</t>
+          <t>Zoom : opérationnel depuis le 15/10</t>
         </is>
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>Big Five (compte Zoom cossi@bigfiveabidjan.com)</t>
+          <t>Équipe (test de la salle)</t>
         </is>
       </c>
       <c r="D7" s="50" t="inlineStr">
@@ -4928,22 +4164,22 @@
       </c>
       <c r="E7" s="50" t="inlineStr">
         <is>
-          <t>Zoom répond « The app has been disabled by the developer » (invalid_client) pour l'app Server-to-Server. ZOOM_SDK_CLIENT_ID est vide et ZOOM_SDK_CLIENT_SECRET a la longueur d'un Client ID : valeurs probablement inversées. La salle reste en simulation.</t>
+          <t>App activée, clés posées, mode réel en production. La session ses-010 a créé sa réunion chez Zoom (83441083225, hôte cossi@). Attention : une session créée depuis un serveur local lancé avant le passage en réel reçoit une réunion fictive — un bandeau le signale désormais.</t>
         </is>
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>COL-05, Z1 à Z9</t>
+          <t>COL-05, Z7 à Z9</t>
         </is>
       </c>
       <c r="G7" s="50" t="inlineStr">
         <is>
-          <t>Sur marketplace.zoom.us : activer l'app Server-to-Server (onglet Activation), relever le Client ID et le Client Secret de l'app Meeting SDK, vérifier la licence Pro. Guide pas à pas : onglet « Passage en production », Z1 à Z3.</t>
-        </is>
-      </c>
-      <c r="H7" s="51" t="inlineStr">
-        <is>
-          <t>BLQ-ZOOM → Captures, ligne 214</t>
+          <t>Tester l'entrée dans la salle (formateur sur ordinateur, apprenant sur mobile), puis reporter et annuler une session réelle.</t>
+        </is>
+      </c>
+      <c r="H7" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4191,12 @@
       </c>
       <c r="B8" s="49" t="inlineStr">
         <is>
-          <t>Envoi d'e-mails : aucun compte d'envoi ni adresse sur le domaine</t>
+          <t>E-mails : branchés par Resend le 15/10</t>
         </is>
       </c>
       <c r="C8" s="50" t="inlineStr">
         <is>
-          <t>Big Five (compte Brevo / Resend / SMTP + accès DNS)</t>
+          <t>Fait (Big Five + dev)</t>
         </is>
       </c>
       <c r="D8" s="50" t="inlineStr">
@@ -4970,22 +4206,22 @@
       </c>
       <c r="E8" s="50" t="inlineStr">
         <is>
-          <t>NOTIFICATIONS_DRIVER=console : les messages sont écrits dans le journal du serveur, aucun ne part.</t>
+          <t>Domaine bigfive.solutions vérifié chez Resend (DKIM, SPF du sous-domaine send) ; réinitialisation délivrée, avis d'annulation envoyé. Deux enregistrements DMARC coexistent sur _dmarc.bigfive.solutions (p=quarantine et p=none).</t>
         </is>
       </c>
       <c r="F8" s="50" t="inlineStr">
         <is>
-          <t>VIT-17, ACH-10, ATT-09, COL-06, SEC-07</t>
+          <t>VIT-17, SEC-07, COL-06</t>
         </is>
       </c>
       <c r="G8" s="50" t="inlineStr">
         <is>
-          <t>Ouvrir un compte d'envoi, poser SPF, DKIM et DMARC sur le domaine, créer l'adresse e-mail E-Masterclass. Le développement branche ensuite le pilote d'envoi (2 jours).</t>
-        </is>
-      </c>
-      <c r="H8" s="51" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → Captures, ligne 37</t>
+          <t>Garder un seul enregistrement DMARC (supprimer « v=DMARC1; p=none; » dans Cloudflare). Créer la boîte contact@bigfiveabidjan.com si elle n'existe pas.</t>
+        </is>
+      </c>
+      <c r="H8" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4233,12 @@
       </c>
       <c r="B9" s="49" t="inlineStr">
         <is>
-          <t>Domaine de production non branché</t>
+          <t>Domaine de production : branché le 15/10</t>
         </is>
       </c>
       <c r="C9" s="50" t="inlineStr">
         <is>
-          <t>Big Five (DNS de bigfive.solutions, chez Cloudflare)</t>
+          <t>Fait</t>
         </is>
       </c>
       <c r="D9" s="50" t="inlineStr">
@@ -5012,7 +4248,7 @@
       </c>
       <c r="E9" s="50" t="inlineStr">
         <is>
-          <t>NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel : sitemap, canonical et QR des attestations portent cette adresse.</t>
+          <t>URL définitive https://emasterclass.bigfive.solutions/ : CNAME chez Cloudflare vers Vercel, HTTPS actif, NUXT_PUBLIC_SITE_URL posé.</t>
         </is>
       </c>
       <c r="F9" s="50" t="inlineStr">
@@ -5022,12 +4258,12 @@
       </c>
       <c r="G9" s="50" t="inlineStr">
         <is>
-          <t>Ajouter le domaine dans Vercel, puis le CNAME emasterclass dans Cloudflare, en « DNS only » ; le développement pose la variable et redéploie.</t>
-        </is>
-      </c>
-      <c r="H9" s="51" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → Captures, ligne 37</t>
+          <t>Reste à déclarer ce domaine dans la Search Console (C10).</t>
+        </is>
+      </c>
+      <c r="H9" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5069,8 +4305,8 @@
       </c>
       <c r="H10" s="51" t="inlineStr">
         <is>
-          <t>BLQ-JURIDIQUE → Captures, ligne 98
-ACH-03 → Captures, ligne 243</t>
+          <t>BLQ-JURIDIQUE → Captures, ligne 127
+ACH-03 → Captures, ligne 272</t>
         </is>
       </c>
     </row>
@@ -5112,7 +4348,7 @@
       </c>
       <c r="H11" s="51" t="inlineStr">
         <is>
-          <t>BLQ-VIDEOS → Captures, ligne 155</t>
+          <t>BLQ-VIDEOS → Captures, ligne 184</t>
         </is>
       </c>
     </row>
@@ -5155,7 +4391,7 @@
       <c r="H12" s="51" t="inlineStr">
         <is>
           <t>BLQ-CATALOGUE → Captures, ligne 4
-ADM-06 → Captures, ligne 378</t>
+ADM-06 → Captures, ligne 519</t>
         </is>
       </c>
     </row>
@@ -5197,7 +4433,7 @@
       </c>
       <c r="H13" s="51" t="inlineStr">
         <is>
-          <t>ATT-05 → Captures, ligne 784</t>
+          <t>ATT-05 → Captures, ligne 925</t>
         </is>
       </c>
     </row>
@@ -5239,7 +4475,7 @@
       </c>
       <c r="H14" s="51" t="inlineStr">
         <is>
-          <t>VIT-15 → Captures, ligne 1178</t>
+          <t>VIT-15 → Captures, ligne 1319</t>
         </is>
       </c>
     </row>
@@ -5281,8 +4517,8 @@
       </c>
       <c r="H15" s="51" t="inlineStr">
         <is>
-          <t>BLQ-GA4 → Captures, ligne 66
-ADM-21 → Captures, ligne 543</t>
+          <t>BLQ-GA4 → Captures, ligne 95
+ADM-21 → Captures, ligne 684</t>
         </is>
       </c>
     </row>
@@ -5331,194 +4567,192 @@
     <row r="17">
       <c r="A17" s="49" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B17" s="49" t="inlineStr">
         <is>
-          <t>Informations contractuelles FeexPay</t>
+          <t>Wave : Clé agrégée Wave non activée</t>
         </is>
       </c>
       <c r="C17" s="50" t="inlineStr">
         <is>
-          <t>Big Five (contrat FeexPay)</t>
+          <t>Big Five (tableau de bord FeexPay)</t>
         </is>
       </c>
       <c r="D17" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E17" s="50" t="inlineStr">
         <is>
-          <t>Taux réel, frais fixes, plafonds, reversement, jeu de test et contact technique non fournis.</t>
+          <t>FeexPay répond « Wave aggregated merchant not configured for this merchant ». La documentation FeexPay situe le réglage dans Configuration › Clé agrégée Wave (« encaisser des paiements Wave en tant que marchand agrégé »).</t>
         </is>
       </c>
       <c r="F17" s="50" t="inlineStr">
         <is>
-          <t>ACH-06, ACH-12, FOR-04</t>
+          <t>ACH-04, ACH-07</t>
         </is>
       </c>
       <c r="G17" s="50" t="inlineStr">
         <is>
-          <t>Voir l'onglet « Paiement — FeexPay », lignes 10 à 19. Poser aussi à FeexPay les 3 questions carte (parcours Djamo, barème carte, webhook carte).</t>
-        </is>
-      </c>
-      <c r="H17" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Activer la Clé agrégée Wave dans FeexPay › Configuration, ou la demander au support FeexPay. Puis FEEXPAY_WAVE_ACTIVE=true sur Vercel et redéployer.</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="inlineStr">
+        <is>
+          <t>BLQ-FEEXPAY → Captures, ligne 66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="49" t="inlineStr">
         <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Informations contractuelles FeexPay</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
+        <is>
+          <t>Big Five (contrat FeexPay)</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="50" t="inlineStr">
+        <is>
+          <t>Taux réel, frais fixes, plafonds, reversement, jeu de test et contact technique non fournis.</t>
+        </is>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>ACH-06, ACH-12, FOR-04</t>
+        </is>
+      </c>
+      <c r="G18" s="50" t="inlineStr">
+        <is>
+          <t>Voir l'onglet « Paiement — FeexPay », lignes 10 à 19. Poser aussi à FeexPay les 3 questions carte (parcours Djamo, barème carte, webhook carte).</t>
+        </is>
+      </c>
+      <c r="H18" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>Sauvegardes de la base</t>
         </is>
       </c>
-      <c r="C18" s="50" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>Big Five (choix de l’offre Supabase)</t>
         </is>
       </c>
-      <c r="D18" s="50" t="inlineStr">
+      <c r="D19" s="50" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="E18" s="50" t="inlineStr">
+      <c r="E19" s="50" t="inlineStr">
         <is>
           <t>L'offre gratuite ne garantit ni sauvegarde ni restauration.</t>
         </is>
       </c>
-      <c r="F18" s="50" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>EXP-06</t>
         </is>
       </c>
-      <c r="G18" s="50" t="inlineStr">
+      <c r="G19" s="50" t="inlineStr">
         <is>
           <t>Arbitrer l'offre Supabase.</t>
         </is>
       </c>
-      <c r="H18" s="50" t="inlineStr">
+      <c r="H19" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>2. Reste au développement</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Blocage</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>Qui doit agir</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>Constaté le</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Ce que l’on constate</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>Cas bloqués</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>Action attendue</t>
         </is>
       </c>
-      <c r="H22" s="32" t="inlineStr">
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>Preuve</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="49" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>/admin/apprenants plante (erreur 500)</t>
-        </is>
-      </c>
-      <c r="C23" s="50" t="inlineStr">
-        <is>
-          <t>Développement</t>
-        </is>
-      </c>
-      <c r="D23" s="50" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="E23" s="50" t="inlineStr">
-        <is>
-          <t>« Cannot read properties of undefined (reading 'length') », app/pages/admin/apprenants.vue:502, sur la base en ligne.</t>
-        </is>
-      </c>
-      <c r="F23" s="50" t="inlineStr">
-        <is>
-          <t>ADM-12, ADM-14</t>
-        </is>
-      </c>
-      <c r="G23" s="50" t="inlineStr">
-        <is>
-          <t>Corriger, puis faire rejouer ADM-12 et ADM-14.</t>
-        </is>
-      </c>
-      <c r="H23" s="51" t="inlineStr">
-        <is>
-          <t>ADM-12 → Captures, ligne 406</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="49" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B24" s="49" t="inlineStr">
         <is>
-          <t>Mot de passe de démonstration encore actif sur un administrateur principal</t>
+          <t>/admin/apprenants plante (erreur 500)</t>
         </is>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>Développement + Big Five</t>
+          <t>Corrigé (27d835b)</t>
         </is>
       </c>
       <c r="D24" s="50" t="inlineStr">
@@ -5528,39 +4762,40 @@
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>cossi@bigfiveabidjan.com s'ouvre avec le mot de passe publié dans le README.</t>
+          <t>« Cannot read properties of undefined (reading 'length') », app/pages/admin/apprenants.vue:502. Cause : une fusion a gardé l'API qui renvoie { apprenants, choix } et repris un écran qui attend une simple liste ; l'écran parcourait l'objet au lieu des apprenants. L'écran lit désormais la liste.</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>SEC-11</t>
+          <t>ADM-12, ADM-14</t>
         </is>
       </c>
       <c r="G24" s="50" t="inlineStr">
         <is>
-          <t>Changer les mots de passe de tous les comptes du jeu de données, retirer celui du README.</t>
-        </is>
-      </c>
-      <c r="H24" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Vérifié le 15/10 sur la base en ligne : liste des 10 comptes, fiche, historique, export CSV (10 lignes, 13 colonnes), formulaire Prénom / Nom. Reste au testeur : créer un apprenant de test (ADM-12), non rejoué pour ne rien écrire en base.</t>
+        </is>
+      </c>
+      <c r="H24" s="51" t="inlineStr">
+        <is>
+          <t>ADM-12 → Captures, ligne 547
+ADM-12-corrige → Captures, ligne 1347</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="49" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B25" s="49" t="inlineStr">
         <is>
-          <t>Séance passée affichée « En direct »</t>
+          <t>Mots de passe de démonstration encore actifs (dont l'administrateur principal)</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Big Five (lancer le script)</t>
         </is>
       </c>
       <c r="D25" s="50" t="inlineStr">
@@ -5570,39 +4805,39 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>La séance du 19/09 affiche « EN DIRECT · 621 h » côté apprenant.</t>
+          <t>Lecture du 15/10 sur la base en ligne : 6 comptes sur 7 acceptent encore le mot de passe commun du jeu de données — cossi@, jeremie.declercq@, houefa@bigfiveabidjan.com, editeur@bigfive.ci, formateur@bigfive.ci, aya@example.ci. Seul jeanluc@ l'a changé.</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
         <is>
-          <t>COL-05</t>
+          <t>SEC-11</t>
         </is>
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>Clore l'affichage à la fin de la séance.</t>
-        </is>
-      </c>
-      <c r="H25" s="51" t="inlineStr">
-        <is>
-          <t>COL-05-seance-passee → Captures, ligne 937</t>
+          <t>Mot de passe retiré du README et du TODO le 15/10. Script prêt : npm run auth:renouveler (lecture seule) puis npm run auth:renouveler -- --appliquer, qui tire un mot de passe aléatoire par compte et l'affiche une seule fois dans le terminal : le reporter dans un gestionnaire, le transmettre à son titulaire. Puis remplacer NUXT_SESSION_PASSWORD sur Vercel pour fermer les sessions ouvertes.</t>
+        </is>
+      </c>
+      <c r="H25" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="49" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B26" s="49" t="inlineStr">
         <is>
-          <t>Rattacher les paiements carte à la commande</t>
+          <t>Séance passée affichée « En direct »</t>
         </is>
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>Développement (après C1)</t>
+          <t>Corrigé (27d835b)</t>
         </is>
       </c>
       <c r="D26" s="50" t="inlineStr">
@@ -5612,39 +4847,40 @@
       </c>
       <c r="E26" s="50" t="inlineStr">
         <is>
-          <t>Le parcours carte du SDK FeexPay n'envoie pas la référence de commande (custom_id) : une carte débitée risquerait de ne pas ouvrir le module.</t>
+          <t>La séance du 19/09 affiche « EN DIRECT · 621 h » côté apprenant.</t>
         </is>
       </c>
       <c r="F26" s="50" t="inlineStr">
         <is>
-          <t>ACH-05</t>
+          <t>COL-05</t>
         </is>
       </c>
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>Vérifier sur un vrai paiement carte ; sinon ouvrir la carte depuis le serveur (docs/paiement-carte-a-ajuster.md, §2).</t>
-        </is>
-      </c>
-      <c r="H26" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Vérifié le 15/10 : la séance du 19/09 affiche « TERMINÉE · 19 septembre à 20:00 » et « Cette séance s'est terminée », bouton d'entrée grisé, y compris pour le formateur et l'administrateur (retouche du bouton à commiter).</t>
+        </is>
+      </c>
+      <c r="H26" s="51" t="inlineStr">
+        <is>
+          <t>COL-05-seance-passee → Captures, ligne 1078
+COL-05-corrige → Captures, ligne 1375</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="49" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B27" s="49" t="inlineStr">
         <is>
-          <t>Relance des commandes en attente</t>
+          <t>Rattacher les paiements carte à la commande</t>
         </is>
       </c>
       <c r="C27" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Développement (après C1)</t>
         </is>
       </c>
       <c r="D27" s="50" t="inlineStr">
@@ -5654,34 +4890,34 @@
       </c>
       <c r="E27" s="50" t="inlineStr">
         <is>
-          <t>Aucune tâche ne relit les commandes restées « En attente ».</t>
+          <t>Le parcours carte du SDK FeexPay n'envoie pas la référence de commande (custom_id) : une carte débitée risquerait de ne pas ouvrir le module.</t>
         </is>
       </c>
       <c r="F27" s="50" t="inlineStr">
         <is>
-          <t>ACH-09</t>
+          <t>ACH-05</t>
         </is>
       </c>
       <c r="G27" s="50" t="inlineStr">
         <is>
-          <t>Tâche planifiée de rapprochement.</t>
-        </is>
-      </c>
-      <c r="H27" s="51" t="inlineStr">
-        <is>
-          <t>ADM-20 → Captures, ligne 434</t>
+          <t>Vérifier sur un vrai paiement carte ; sinon ouvrir la carte depuis le serveur (docs/paiement-carte-a-ajuster.md, §2).</t>
+        </is>
+      </c>
+      <c r="H27" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="49" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>Coaching privé absent de /admin/transactions</t>
+          <t>Relance des commandes en attente</t>
         </is>
       </c>
       <c r="C28" s="50" t="inlineStr">
@@ -5696,34 +4932,34 @@
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>Ces paiements ne sont suivis que dans la console FeexPay.</t>
+          <t>Aucune tâche ne relit les commandes restées « En attente ».</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
         <is>
-          <t>PRI-08</t>
+          <t>ACH-09</t>
         </is>
       </c>
       <c r="G28" s="50" t="inlineStr">
         <is>
-          <t>Les faire apparaître dans Transactions.</t>
-        </is>
-      </c>
-      <c r="H28" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tâche planifiée de rapprochement.</t>
+        </is>
+      </c>
+      <c r="H28" s="51" t="inlineStr">
+        <is>
+          <t>ADM-20 → Captures, ligne 575</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="49" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t>Contrôle des types</t>
+          <t>Coaching privé absent de /admin/transactions</t>
         </is>
       </c>
       <c r="C29" s="50" t="inlineStr">
@@ -5738,17 +4974,17 @@
       </c>
       <c r="E29" s="50" t="inlineStr">
         <is>
-          <t>npm run typecheck : 5 erreurs sur Referentiels.vue (sans effet sur le build).</t>
+          <t>Ces paiements ne sont suivis que dans la console FeexPay.</t>
         </is>
       </c>
       <c r="F29" s="50" t="inlineStr">
         <is>
-          <t>EXP-03</t>
+          <t>PRI-08</t>
         </is>
       </c>
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>Corriger le typage.</t>
+          <t>Les faire apparaître dans Transactions.</t>
         </is>
       </c>
       <c r="H29" s="50" t="inlineStr">
@@ -5760,12 +4996,12 @@
     <row r="30">
       <c r="A30" s="49" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B30" s="49" t="inlineStr">
         <is>
-          <t>Droit de lecture de la clé publique sur 2 tables</t>
+          <t>Contrôle des types</t>
         </is>
       </c>
       <c r="C30" s="50" t="inlineStr">
@@ -5780,17 +5016,17 @@
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>visionnages et reglages_attestation répondent 200 (vide) au lieu de 401.</t>
+          <t>npm run typecheck : 5 erreurs sur Referentiels.vue (sans effet sur le build).</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
         <is>
-          <t>SEC-09</t>
+          <t>EXP-03</t>
         </is>
       </c>
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>Retirer le droit, comme sur les 43 autres tables.</t>
+          <t>Corriger le typage.</t>
         </is>
       </c>
       <c r="H30" s="50" t="inlineStr">
@@ -5802,42 +5038,428 @@
     <row r="31">
       <c r="A31" s="49" t="inlineStr">
         <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>Droit de lecture de la clé publique sur 2 tables</t>
+        </is>
+      </c>
+      <c r="C31" s="50" t="inlineStr">
+        <is>
+          <t>Développement</t>
+        </is>
+      </c>
+      <c r="D31" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="50" t="inlineStr">
+        <is>
+          <t>visionnages et reglages_attestation répondent 200 (vide) au lieu de 401.</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>SEC-09</t>
+        </is>
+      </c>
+      <c r="G31" s="50" t="inlineStr">
+        <is>
+          <t>Retirer le droit, comme sur les 43 autres tables.</t>
+        </is>
+      </c>
+      <c r="H31" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
           <t>D9</t>
         </is>
       </c>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>Pilote d'envoi d'e-mails</t>
-        </is>
-      </c>
-      <c r="C31" s="50" t="inlineStr">
-        <is>
-          <t>Développement (après C3)</t>
-        </is>
-      </c>
-      <c r="D31" s="50" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="E31" s="50" t="inlineStr">
-        <is>
-          <t>Seul le pilote « console » existe.</t>
-        </is>
-      </c>
-      <c r="F31" s="50" t="inlineStr">
-        <is>
-          <t>VIT-17, ACH-10, ATT-09, SEC-07</t>
-        </is>
-      </c>
-      <c r="G31" s="50" t="inlineStr">
-        <is>
-          <t>Écrire le pilote du prestataire retenu (2 jours).</t>
-        </is>
-      </c>
-      <c r="H31" s="50" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>E-mails de confirmation d'achat et d'attestation</t>
+        </is>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>Développé, à fusionner</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="50" t="inlineStr">
+        <is>
+          <t>Les deux modèles sont écrits (commit 5b98316, branche jl/practical-chatelet-e7dbbe) ; ils ne sont pas encore dans main.</t>
+        </is>
+      </c>
+      <c r="F32" s="50" t="inlineStr">
+        <is>
+          <t>ACH-10, ATT-09</t>
+        </is>
+      </c>
+      <c r="G32" s="50" t="inlineStr">
+        <is>
+          <t>Fusionner la branche dans main, déployer, puis vérifier les deux e-mails sur un vrai achat et une vraie délivrance.</t>
+        </is>
+      </c>
+      <c r="H32" s="50" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>3. Corrigé le 15/10 au soir (paiement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Blocage</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Qui doit agir</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>Constaté le</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>Ce que l’on constate</t>
+        </is>
+      </c>
+      <c r="F36" s="32" t="inlineStr">
+        <is>
+          <t>Cas bloqués</t>
+        </is>
+      </c>
+      <c r="G36" s="32" t="inlineStr">
+        <is>
+          <t>Action attendue</t>
+        </is>
+      </c>
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>Preuve</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Description de paiement refusée par FeexPay</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (123ab6b, 3360135)</t>
+        </is>
+      </c>
+      <c r="D37" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="50" t="inlineStr">
+        <is>
+          <t>FeexPay refuse plus de 40 caractères et les caractères spéciaux : 10 modules sur 18 ne pouvaient pas être payés.</t>
+        </is>
+      </c>
+      <c r="F37" s="50" t="inlineStr">
+        <is>
+          <t>ACH-05</t>
+        </is>
+      </c>
+      <c r="G37" s="50" t="inlineStr">
+        <is>
+          <t>Description raccourcie et nettoyée.</t>
+        </is>
+      </c>
+      <c r="H37" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>Page 404 « /achat/undefined » sur Wave</t>
+        </is>
+      </c>
+      <c r="C38" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (2a2e1b3)</t>
+        </is>
+      </c>
+      <c r="D38" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="50" t="inlineStr">
+        <is>
+          <t>Le SDK ouvrait une adresse vide quand FeexPay refusait Wave.</t>
+        </is>
+      </c>
+      <c r="F38" s="50" t="inlineStr">
+        <is>
+          <t>ACH-04</t>
+        </is>
+      </c>
+      <c r="G38" s="50" t="inlineStr">
+        <is>
+          <t>Le cadre vide est retiré et un message explicite s’affiche.</t>
+        </is>
+      </c>
+      <c r="H38" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>Numéro saisi deux fois</t>
+        </is>
+      </c>
+      <c r="C39" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (e6f4476)</t>
+        </is>
+      </c>
+      <c r="D39" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="50" t="inlineStr">
+        <is>
+          <t>Le SDK ignore le numéro, le nom et l'e-mail transmis.</t>
+        </is>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
+        <is>
+          <t>ACH-04</t>
+        </is>
+      </c>
+      <c r="G39" s="50" t="inlineStr">
+        <is>
+          <t>La fenêtre FeexPay est pré-remplie, opérateur compris.</t>
+        </is>
+      </c>
+      <c r="H39" s="51" t="inlineStr">
+        <is>
+          <t>ACH-04-prefill → Captures, ligne 378</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr">
+        <is>
+          <t>Opérateur enregistré « Orange Money » pour un paiement MTN</t>
+        </is>
+      </c>
+      <c r="C40" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (e6f4476)</t>
+        </is>
+      </c>
+      <c r="D40" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="50" t="inlineStr">
+        <is>
+          <t>FeexPay ne renvoie pas l'opérateur d'un paiement Mobile Money.</t>
+        </is>
+      </c>
+      <c r="F40" s="50" t="inlineStr">
+        <is>
+          <t>ADM-20</t>
+        </is>
+      </c>
+      <c r="G40" s="50" t="inlineStr">
+        <is>
+          <t>L'opérateur se déduit du numéro payeur (01 Moov, 05 MTN, 07 Orange).</t>
+        </is>
+      </c>
+      <c r="H40" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>Message d’échec générique</t>
+        </is>
+      </c>
+      <c r="C41" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (e2706b6, e6f4476)</t>
+        </is>
+      </c>
+      <c r="D41" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="50" t="inlineStr">
+        <is>
+          <t>« Erreur chez le prestataire » au lieu du motif réel.</t>
+        </is>
+      </c>
+      <c r="F41" s="50" t="inlineStr">
+        <is>
+          <t>ACH-06</t>
+        </is>
+      </c>
+      <c r="G41" s="50" t="inlineStr">
+        <is>
+          <t>Le motif FeexPay est lu, traduit et tracé.</t>
+        </is>
+      </c>
+      <c r="H41" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>Retour d’Orange Money vers app-v2.feexpay.me</t>
+        </is>
+      </c>
+      <c r="C42" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (f6126d7)</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="50" t="inlineStr">
+        <is>
+          <t>Le SDK n'envoie pas return_url pour Orange.</t>
+        </is>
+      </c>
+      <c r="F42" s="50" t="inlineStr">
+        <is>
+          <t>ACH-05</t>
+        </is>
+      </c>
+      <c r="G42" s="50" t="inlineStr">
+        <is>
+          <t>Les adresses de retour du site sont ajoutées à la requête.</t>
+        </is>
+      </c>
+      <c r="H42" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>Wave et carte invisibles</t>
+        </is>
+      </c>
+      <c r="C43" s="50" t="inlineStr">
+        <is>
+          <t>Corrigé (e6f4476)</t>
+        </is>
+      </c>
+      <c r="D43" s="50" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="50" t="inlineStr">
+        <is>
+          <t>Masqués tant que FeexPay ne les ouvrait pas.</t>
+        </is>
+      </c>
+      <c r="F43" s="50" t="inlineStr">
+        <is>
+          <t>ACH-04</t>
+        </is>
+      </c>
+      <c r="G43" s="50" t="inlineStr">
+        <is>
+          <t>« Bientôt disponible » avec la raison et un renvoi vers le Mobile Money.</t>
+        </is>
+      </c>
+      <c r="H43" s="51" t="inlineStr">
+        <is>
+          <t>ACH-04-wave → Captures, ligne 414
+ACH-04-carte → Captures, ligne 340</t>
         </is>
       </c>
     </row>
@@ -5846,19 +5468,19 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H6" location="'Captures'!B126" display="BLQ-KYC → Captures, ligne 126&#10;ADM-20 → Captures, ligne 434"/>
-    <hyperlink ref="H7" location="'Captures'!B214" display="BLQ-ZOOM → Captures, ligne 214"/>
-    <hyperlink ref="H8" location="'Captures'!B37" display="BLQ-CONFIG → Captures, ligne 37"/>
-    <hyperlink ref="H9" location="'Captures'!B37" display="BLQ-CONFIG → Captures, ligne 37"/>
-    <hyperlink ref="H10" location="'Captures'!B98" display="BLQ-JURIDIQUE → Captures, ligne 98&#10;ACH-03 → Captures, ligne 243"/>
-    <hyperlink ref="H11" location="'Captures'!B155" display="BLQ-VIDEOS → Captures, ligne 155"/>
-    <hyperlink ref="H12" location="'Captures'!B4" display="BLQ-CATALOGUE → Captures, ligne 4&#10;ADM-06 → Captures, ligne 378"/>
-    <hyperlink ref="H13" location="'Captures'!B784" display="ATT-05 → Captures, ligne 784"/>
-    <hyperlink ref="H14" location="'Captures'!B1178" display="VIT-15 → Captures, ligne 1178"/>
-    <hyperlink ref="H15" location="'Captures'!B66" display="BLQ-GA4 → Captures, ligne 66&#10;ADM-21 → Captures, ligne 543"/>
-    <hyperlink ref="H23" location="'Captures'!B406" display="ADM-12 → Captures, ligne 406"/>
-    <hyperlink ref="H25" location="'Captures'!B937" display="COL-05-seance-passee → Captures, ligne 937"/>
-    <hyperlink ref="H27" location="'Captures'!B434" display="ADM-20 → Captures, ligne 434"/>
+    <hyperlink ref="H6" location="'Captures'!B155" display="BLQ-KYC → Captures, ligne 155&#10;ADM-20 → Captures, ligne 575"/>
+    <hyperlink ref="H10" location="'Captures'!B127" display="BLQ-JURIDIQUE → Captures, ligne 127&#10;ACH-03 → Captures, ligne 272"/>
+    <hyperlink ref="H11" location="'Captures'!B184" display="BLQ-VIDEOS → Captures, ligne 184"/>
+    <hyperlink ref="H12" location="'Captures'!B4" display="BLQ-CATALOGUE → Captures, ligne 4&#10;ADM-06 → Captures, ligne 519"/>
+    <hyperlink ref="H13" location="'Captures'!B925" display="ATT-05 → Captures, ligne 925"/>
+    <hyperlink ref="H14" location="'Captures'!B1319" display="VIT-15 → Captures, ligne 1319"/>
+    <hyperlink ref="H15" location="'Captures'!B95" display="BLQ-GA4 → Captures, ligne 95&#10;ADM-21 → Captures, ligne 684"/>
+    <hyperlink ref="H17" location="'Captures'!B66" display="BLQ-FEEXPAY → Captures, ligne 66"/>
+    <hyperlink ref="H24" location="'Captures'!B547" display="ADM-12 → Captures, ligne 547"/>
+    <hyperlink ref="H26" location="'Captures'!B1078" display="COL-05-seance-passee → Captures, ligne 1078"/>
+    <hyperlink ref="H28" location="'Captures'!B575" display="ADM-20 → Captures, ligne 575"/>
+    <hyperlink ref="H39" location="'Captures'!B378" display="ACH-04-prefill → Captures, ligne 378"/>
+    <hyperlink ref="H43" location="'Captures'!B414" display="ACH-04-wave → Captures, ligne 414&#10;ACH-04-carte → Captures, ligne 340"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5904,7 +5526,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -6585,7 +6206,7 @@
       </c>
       <c r="O15" s="53" t="inlineStr">
         <is>
-          <t>VIT-11-accueil → ligne 1122
+          <t>VIT-11-accueil → ligne 1263
 BLQ-CATALOGUE → ligne 4</t>
         </is>
       </c>
@@ -6651,7 +6272,7 @@
       </c>
       <c r="O16" s="53" t="inlineStr">
         <is>
-          <t>VIT-12-fiche → ligne 1150</t>
+          <t>VIT-12-fiche → ligne 1291</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6456,7 @@
       </c>
       <c r="O19" s="53" t="inlineStr">
         <is>
-          <t>VIT-15 → ligne 1178</t>
+          <t>VIT-15 → ligne 1319</t>
         </is>
       </c>
     </row>
@@ -6953,21 +6574,17 @@
           <t>Contenu client : créer l'adresse sur le domaine. L'envoi lui-même attend un pilote d'e-mail réel (server/utils/notifications.ts n'écrit qu'en console).</t>
         </is>
       </c>
-      <c r="M21" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
         </is>
       </c>
       <c r="N21" s="33" t="inlineStr">
         <is>
-          <t>Le formulaire fonctionne mais aucun e-mail ne part : pas de compte d'envoi ni d'adresse sur le domaine (NOTIFICATIONS_DRIVER=console).</t>
-        </is>
-      </c>
-      <c r="O21" s="53" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → ligne 37</t>
-        </is>
-      </c>
+          <t>Envoi branché par Resend depuis le 15/10 : le message part vers contact@bigfiveabidjan.com (CONTACT_DESTINATAIRE), avec un accusé de réception à l'expéditeur. Pas encore essayé en ligne.</t>
+        </is>
+      </c>
+      <c r="O21" s="33" t="n"/>
     </row>
     <row r="22" ht="25.5" customHeight="1" s="31">
       <c r="A22" s="33" t="inlineStr">
@@ -7140,7 +6757,7 @@
       </c>
       <c r="O24" s="53" t="inlineStr">
         <is>
-          <t>BLQ-JURIDIQUE → ligne 98</t>
+          <t>BLQ-JURIDIQUE → ligne 127</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7205,7 @@
       </c>
       <c r="O32" s="53" t="inlineStr">
         <is>
-          <t>ACH-03 → ligne 243</t>
+          <t>ACH-03 → ligne 272</t>
         </is>
       </c>
     </row>
@@ -7648,13 +7265,15 @@
       </c>
       <c r="N33" s="33" t="inlineStr">
         <is>
-          <t>Mobile Money et Wave proposés, chacun avec ses consignes. Visa et Djamo sont volontairement masqués : FeexPay refuse la carte tant que le KYC carte de la boutique est en brouillon (réponse 403 CARD_PAYMENT_NOT_AUTHORIZED du 15/10).</t>
+          <t>Les quatre moyens sont affichés. Mobile Money (Orange, MTN, Moov) est ouvert ; Wave, Djamo et Visa portent « Bientôt disponible » et expliquent pourquoi (Wave non activé chez FeexPay, KYC carte en brouillon), avec un bouton « Payer par Mobile Money ». La fenêtre FeexPay est pré-remplie : nom, e-mail, numéro et opérateur déduit du numéro (correctifs du 15/10 au soir).</t>
         </is>
       </c>
       <c r="O33" s="53" t="inlineStr">
         <is>
-          <t>ACH-04 → ligne 277
-BLQ-KYC → ligne 126</t>
+          <t>ACH-04 → ligne 306
+ACH-04-wave → ligne 414
+ACH-04-carte → ligne 340
+ACH-04-prefill → ligne 378</t>
         </is>
       </c>
     </row>
@@ -7719,20 +7338,20 @@
           <t>Corrigé le 13/10 (b977ad3) : consignes, numéro et écran d'attente propres à chaque moyen (Mobile Money, Wave, Djamo, Visa). L'échange passe désormais par le widget FeexPay (sandbox en local, live en production). À retester.</t>
         </is>
       </c>
-      <c r="M34" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M34" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N34" s="33" t="inlineStr">
         <is>
-          <t>Mobile Money et Wave passent par FeexPay en live. Par carte, les essais restent « En attente » (4 commandes Visa / Djamo visibles dans /admin/transactions) : FeexPay n'autorise pas la carte sur la boutique.</t>
+          <t>Paiement réel validé de bout en bout le 15/10 : Orange Money 200 F à 19:18 (CMD-MV9X8GWL-50A6) et MTN 200 F à 19:25 (CMD-MV9XID99-CFWZ) réussis chez FeexPay, commandes confirmées, modules ouverts dans l'espace de l'acheteur, opérateur bien enregistré. Les refus du payeur (« solde ou plafond ») sont affichés et tracés. Deux défauts corrigés en route : description de plus de 40 caractères refusée par FeexPay, retour d'Orange Money vers app-v2.feexpay.me.</t>
         </is>
       </c>
       <c r="O34" s="53" t="inlineStr">
         <is>
-          <t>ADM-20 → ligne 434
-BLQ-KYC → ligne 126</t>
+          <t>BLQ-FEEXPAY → ligne 66
+ADM-20 → ligne 575</t>
         </is>
       </c>
     </row>
@@ -7793,9 +7412,21 @@
           <t>Les motifs viennent désormais de FeexPay (codeEchecDepuisMotif, server/utils/feexpay.ts). Ils se recettent avec le jeu de test du prestataire, ou en production avec un vrai refus (onglet « Passage en production »).</t>
         </is>
       </c>
-      <c r="M35" s="33" t="n"/>
-      <c r="N35" s="33" t="n"/>
-      <c r="O35" s="33" t="n"/>
+      <c r="M35" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" s="33" t="inlineStr">
+        <is>
+          <t>Les motifs viennent de FeexPay et sont explicites : le refus MTN du 15/10 est affiché « Solde insuffisant ou plafond atteint », avec la consigne ; un code FeexPay inconnu est cité tel quel. Au retour d'une page Orange ou Wave en échec : « Paiement annulé ».</t>
+        </is>
+      </c>
+      <c r="O35" s="53" t="inlineStr">
+        <is>
+          <t>BLQ-FEEXPAY → ligne 66</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="31">
       <c r="A36" s="33" t="inlineStr">
@@ -7857,12 +7488,13 @@
       </c>
       <c r="N36" s="33" t="inlineStr">
         <is>
-          <t>Encaissement live en place pour Mobile Money et Wave. Carte : dossier KYC carte à faire valider chez FeexPay (card_kyc_status : draft).</t>
+          <t>Encaissement live ouvert pour Orange, MTN et Moov CI. Wave : « Wave aggregated merchant not configured » — la Clé agrégée Wave est à activer dans FeexPay › Configuration. Carte : KYC carte en brouillon (card_kyc_status : draft).</t>
         </is>
       </c>
       <c r="O36" s="53" t="inlineStr">
         <is>
-          <t>BLQ-KYC → ligne 126</t>
+          <t>BLQ-FEEXPAY → ligne 66
+BLQ-KYC → ligne 155</t>
         </is>
       </c>
     </row>
@@ -7919,9 +7551,21 @@
           <t>Endpoint en place : /api/paiements/feexpay/webhook, idempotent. Il est protégé par une clé (FEEXPAY_WEBHOOK_CLE, en-tête Bearer ou ?cle=) et non par une signature FeexPay ; il ne fait que déclencher une relecture du statut chez FeexPay, ce qui limite le risque.</t>
         </is>
       </c>
-      <c r="M37" s="33" t="n"/>
-      <c r="N37" s="33" t="n"/>
-      <c r="O37" s="33" t="n"/>
+      <c r="M37" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" s="33" t="inlineStr">
+        <is>
+          <t>Webhook opérationnel en production : appelé par FeexPay le 15/10 (HTTP 200, clé Bearer), il a enregistré la transaction MTN « échouée · solde insuffisant ». Il refuse un appel sans clé (401).</t>
+        </is>
+      </c>
+      <c r="O37" s="53" t="inlineStr">
+        <is>
+          <t>BLQ-FEEXPAY → ligne 66</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="31">
       <c r="A38" s="33" t="inlineStr">
@@ -8029,21 +7673,17 @@
       <c r="J39" s="33" t="n"/>
       <c r="K39" s="33" t="n"/>
       <c r="L39" s="33" t="n"/>
-      <c r="M39" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M39" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
         </is>
       </c>
       <c r="N39" s="33" t="inlineStr">
         <is>
-          <t>Aucun e-mail ne part tant qu'aucun prestataire d'envoi n'est fourni.</t>
-        </is>
-      </c>
-      <c r="O39" s="53" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → ligne 37</t>
-        </is>
-      </c>
+          <t>Développé le 15/10 (commit 5b98316, branche jl/practical-chatelet-e7dbbe) : e-mail de confirmation d'achat avec module ou séance, montant, moyen et référence, envoyé une seule fois par commande. Pas encore fusionné dans main ni déployé : à retester en ligne après fusion, avec un vrai paiement.</t>
+        </is>
+      </c>
+      <c r="O39" s="33" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="31">
       <c r="A40" s="33" t="inlineStr">
@@ -8171,7 +7811,7 @@
       </c>
       <c r="O41" s="53" t="inlineStr">
         <is>
-          <t>ACH-12 → ligne 311</t>
+          <t>ACH-12 → ligne 452</t>
         </is>
       </c>
     </row>
@@ -8354,7 +7994,7 @@
       </c>
       <c r="O44" s="53" t="inlineStr">
         <is>
-          <t>APP-03 → ligne 613</t>
+          <t>APP-03 → ligne 754</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8125,7 @@
       </c>
       <c r="O46" s="53" t="inlineStr">
         <is>
-          <t>APP-05 → ligne 641</t>
+          <t>APP-05 → ligne 782</t>
         </is>
       </c>
     </row>
@@ -8616,8 +8256,8 @@
       </c>
       <c r="O48" s="53" t="inlineStr">
         <is>
-          <t>APP-07 → ligne 669
-APP-07-mobile → ligne 697</t>
+          <t>APP-07 → ligne 810
+APP-07-mobile → ligne 838</t>
         </is>
       </c>
     </row>
@@ -9240,7 +8880,7 @@
       </c>
       <c r="O59" s="53" t="inlineStr">
         <is>
-          <t>BLQ-VIDEOS → ligne 155</t>
+          <t>BLQ-VIDEOS → ligne 184</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9087,7 @@
       </c>
       <c r="O62" s="53" t="inlineStr">
         <is>
-          <t>COL-01 → ligne 877</t>
+          <t>COL-01 → ligne 1018</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9217,7 @@
       </c>
       <c r="O64" s="53" t="inlineStr">
         <is>
-          <t>COL-03 → ligne 909</t>
+          <t>COL-03 → ligne 1050</t>
         </is>
       </c>
     </row>
@@ -9687,20 +9327,19 @@
           <t>Développé depuis le 02/09 : Zoom Meeting SDK intégré (app/composables/useZoom.ts, /api/zoom/signature), réunions créées automatiquement. En mode simulation tant que ZOOM_MODE=live et les clés ne sont pas posés (onglet « Passage en production »).</t>
         </is>
       </c>
-      <c r="M66" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M66" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>Zoom : l'app Server-to-Server existe mais est désactivée (« The app has been disabled by the developer ») et le Client ID du Meeting SDK manque. Défaut constaté en plus : une séance passée (19/09) s'affiche « EN DIRECT · 621 h » (reste dev).</t>
+          <t>Zoom en réel depuis le 15/10. Création automatique validée : la session ses-010 créée depuis le site à 19:53 a reçu la réunion 83441083225, présente chez Zoom sous le compte cossi@bigfiveabidjan.com (2 h, salle d'attente). Restent à dérouler : entrée formateur et apprenant depuis la plateforme, report et annulation d'une réunion réelle. Une séance passée s'affichait « EN DIRECT · 621 h » : corrigé (27d835b) et vérifié le 15/10, elle affiche « TERMINÉE · 19 septembre à 20:00 ».</t>
         </is>
       </c>
       <c r="O66" s="53" t="inlineStr">
         <is>
-          <t>BLQ-ZOOM → ligne 214
-COL-05-seance-passee → ligne 937</t>
+          <t>COL-05-seance-passee → ligne 1078 · COL-05-corrige → ligne 1375</t>
         </is>
       </c>
     </row>
@@ -9753,19 +9392,19 @@
       <c r="J67" s="33" t="n"/>
       <c r="K67" s="33" t="n"/>
       <c r="L67" s="33" t="n"/>
-      <c r="M67" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M67" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N67" s="33" t="inlineStr">
         <is>
-          <t>Annulation journalisée et notifiée « email + WhatsApp » à l'écran, mais aucun envoi réel sans prestataire.</t>
+          <t>Annulation journalisée et notifiée : l'avis « Session de coaching annulée » est parti par Resend le 15/10 à 19:53 (WhatsApp : pas encore de compte).</t>
         </is>
       </c>
       <c r="O67" s="53" t="inlineStr">
         <is>
-          <t>COL-01 → ligne 877</t>
+          <t>COL-01 → ligne 1018</t>
         </is>
       </c>
     </row>
@@ -10001,8 +9640,8 @@
       </c>
       <c r="O71" s="53" t="inlineStr">
         <is>
-          <t>PRI-02 → ligne 1021
-PRI-02-admin → ligne 1049</t>
+          <t>PRI-02 → ligne 1162
+PRI-02-admin → ligne 1190</t>
         </is>
       </c>
     </row>
@@ -10132,7 +9771,7 @@
       </c>
       <c r="O73" s="53" t="inlineStr">
         <is>
-          <t>PRI-04 → ligne 1094</t>
+          <t>PRI-04 → ligne 1235</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10276,7 @@
       </c>
       <c r="O82" s="53" t="inlineStr">
         <is>
-          <t>ATT-05 → ligne 784</t>
+          <t>ATT-05 → ligne 925</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10353,7 @@
       </c>
       <c r="O83" s="53" t="inlineStr">
         <is>
-          <t>ATT-07 → ligne 849</t>
+          <t>ATT-07 → ligne 990</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10426,7 @@
       </c>
       <c r="O84" s="53" t="inlineStr">
         <is>
-          <t>ATT-07 → ligne 849</t>
+          <t>ATT-07 → ligne 990</t>
         </is>
       </c>
     </row>
@@ -10893,21 +10532,17 @@
       <c r="J86" s="33" t="n"/>
       <c r="K86" s="33" t="n"/>
       <c r="L86" s="33" t="n"/>
-      <c r="M86" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M86" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
         </is>
       </c>
       <c r="N86" s="33" t="inlineStr">
         <is>
-          <t>Pas d'envoi d'e-mail sans prestataire.</t>
-        </is>
-      </c>
-      <c r="O86" s="53" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → ligne 37</t>
-        </is>
-      </c>
+          <t>Développé le 15/10 (commit 5b98316, même branche) : e-mail d'attestation avec le numéro EMBF, le lien vers l'attestation et le lien de vérification, envoyé à la première délivrance. À retester en ligne après fusion.</t>
+        </is>
+      </c>
+      <c r="O86" s="33" t="n"/>
     </row>
     <row r="87" ht="27" customHeight="1" s="31">
       <c r="A87" s="33" t="inlineStr">
@@ -11186,8 +10821,8 @@
       </c>
       <c r="O91" s="53" t="inlineStr">
         <is>
-          <t>FOR-05 → ligne 965
-FOR-05-releve → ligne 993</t>
+          <t>FOR-05 → ligne 1106
+FOR-05-releve → ligne 1134</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11270,7 @@
       </c>
       <c r="O99" s="53" t="inlineStr">
         <is>
-          <t>ADM-05 → ligne 350</t>
+          <t>ADM-05 → ligne 491</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11347,7 @@
       </c>
       <c r="O100" s="53" t="inlineStr">
         <is>
-          <t>ADM-06 → ligne 378</t>
+          <t>ADM-06 → ligne 519</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11424,7 @@
       </c>
       <c r="O101" s="53" t="inlineStr">
         <is>
-          <t>ADM-06 → ligne 378</t>
+          <t>ADM-06 → ligne 519</t>
         </is>
       </c>
     </row>
@@ -12068,17 +11703,17 @@
       </c>
       <c r="M106" s="56" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>À retester</t>
         </is>
       </c>
       <c r="N106" s="33" t="inlineStr">
         <is>
-          <t>Nouveau défaut du 15/10 : /admin/apprenants répond « 500 — Cannot read properties of undefined (reading 'length') » (app/pages/admin/apprenants.vue:502) sur la base en ligne. La création d'apprenant ne peut pas être retestée tant que l'écran ne s'affiche pas. Reste dev.</t>
+          <t>Défaut du 15/10 (500 sur /admin/apprenants) corrigé le soir même (27d835b) et vérifié sur la base en ligne : liste, fiche, historique et formulaire Prénom / Nom s'affichent. La création elle-même reste à rejouer par le testeur avec un compte de test.</t>
         </is>
       </c>
       <c r="O106" s="53" t="inlineStr">
         <is>
-          <t>ADM-12 → ligne 406</t>
+          <t>ADM-12 → ligne 547 · ADM-12-corrige → ligne 1347</t>
         </is>
       </c>
     </row>
@@ -12190,17 +11825,17 @@
       </c>
       <c r="M108" s="56" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
         <is>
-          <t>Même écran que ADM-12 : l'export CSV est inaccessible tant que /admin/apprenants plante.</t>
+          <t>Corrigé avec ADM-12 : l'export CSV produit les 10 comptes affichés (13 colonnes), filtres respectés. Vérifié le 15/10 au soir.</t>
         </is>
       </c>
       <c r="O108" s="53" t="inlineStr">
         <is>
-          <t>ADM-12 → ligne 406</t>
+          <t>ADM-12-corrige → ligne 1347</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12014,7 @@
       </c>
       <c r="O111" s="53" t="inlineStr">
         <is>
-          <t>BLQ-GA4 → ligne 66</t>
+          <t>BLQ-GA4 → ligne 95</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12087,7 @@
       </c>
       <c r="O112" s="53" t="inlineStr">
         <is>
-          <t>BLQ-GA4 → ligne 66</t>
+          <t>BLQ-GA4 → ligne 95</t>
         </is>
       </c>
     </row>
@@ -12582,8 +12217,8 @@
       </c>
       <c r="O114" s="53" t="inlineStr">
         <is>
-          <t>ADM-20 → ligne 434
-ADM-20-editeur → ligne 515</t>
+          <t>ADM-20 → ligne 575
+ADM-20-editeur → ligne 656</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12295,7 @@
       </c>
       <c r="O115" s="53" t="inlineStr">
         <is>
-          <t>ADM-21 → ligne 543</t>
+          <t>ADM-21 → ligne 684</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12372,7 @@
       </c>
       <c r="O116" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 571</t>
+          <t>ADM-22 → ligne 712</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12449,7 @@
       </c>
       <c r="O117" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 571</t>
+          <t>ADM-22 → ligne 712</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12526,7 @@
       </c>
       <c r="O118" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 571</t>
+          <t>ADM-22 → ligne 712</t>
         </is>
       </c>
     </row>
@@ -13021,7 +12656,7 @@
       </c>
       <c r="O120" s="53" t="inlineStr">
         <is>
-          <t>ACH-12 → ligne 311</t>
+          <t>ACH-12 → ligne 452</t>
         </is>
       </c>
     </row>
@@ -13485,21 +13120,17 @@
         </is>
       </c>
       <c r="L128" s="33" t="n"/>
-      <c r="M128" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — prestataire</t>
+      <c r="M128" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N128" s="33" t="inlineStr">
         <is>
-          <t>Le lien de réinitialisation n'est pas envoyé sans prestataire d'e-mail.</t>
-        </is>
-      </c>
-      <c r="O128" s="53" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → ligne 37</t>
-        </is>
-      </c>
+          <t>Lien de réinitialisation envoyé par Resend et délivré le 15/10 (18:14) depuis ne-pas-repondre@bigfive.solutions ; le lien a ouvert la page de réinitialisation.</t>
+        </is>
+      </c>
+      <c r="O128" s="33" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="31">
       <c r="A129" s="33" t="inlineStr">
@@ -13740,7 +13371,7 @@
       </c>
       <c r="N132" s="33" t="inlineStr">
         <is>
-          <t>Le 15/10, le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié dans le README. À changer immédiatement (jeanluc@ a déjà été changé).</t>
+          <t>Le 15/10, 6 comptes sur 7 acceptent encore le mot de passe de démonstration, dont l'administrateur principal cossi@bigfiveabidjan.com (seul jeanluc@ a été changé). Retiré du README le 15/10 ; script npm run auth:renouveler prêt, à lancer par Big Five (voir « En attente client », D2).</t>
         </is>
       </c>
       <c r="O132" s="33" t="n"/>
@@ -14416,7 +14047,7 @@
       </c>
       <c r="O143" s="53" t="inlineStr">
         <is>
-          <t>BLQ-GA4 → ligne 66</t>
+          <t>BLQ-GA4 → ligne 95</t>
         </is>
       </c>
     </row>
@@ -14725,21 +14356,17 @@
       </c>
       <c r="K148" s="33" t="n"/>
       <c r="L148" s="33" t="n"/>
-      <c r="M148" s="54" t="inlineStr">
-        <is>
-          <t>Bloqué — client</t>
+      <c r="M148" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N148" s="33" t="inlineStr">
         <is>
-          <t>emasterclass.bigfive.solutions n'est pas branché ; NUXT_PUBLIC_SITE_URL pointe vers l'URL Vercel.</t>
-        </is>
-      </c>
-      <c r="O148" s="53" t="inlineStr">
-        <is>
-          <t>BLQ-CONFIG → ligne 37</t>
-        </is>
-      </c>
+          <t>URL définitive : https://emasterclass.bigfive.solutions/ — branchée sur Vercel (CNAME Cloudflare), HTTPS actif, NUXT_PUBLIC_SITE_URL posé : sitemap, canonical, QR des attestations, webhook FeexPay, retour Orange et lecture des vidéos sur ce domaine (vérifié le 15/10).</t>
+        </is>
+      </c>
+      <c r="O148" s="33" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="31">
       <c r="A149" s="33" t="inlineStr">
@@ -15720,52 +15347,49 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="O15" location="'Captures'!B1122" display="VIT-11-accueil → ligne 1122&#10;BLQ-CATALOGUE → ligne 4"/>
-    <hyperlink ref="O16" location="'Captures'!B1150" display="VIT-12-fiche → ligne 1150"/>
+    <hyperlink ref="O15" location="'Captures'!B1263" display="VIT-11-accueil → ligne 1263&#10;BLQ-CATALOGUE → ligne 4"/>
+    <hyperlink ref="O16" location="'Captures'!B1291" display="VIT-12-fiche → ligne 1291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId1"/>
-    <hyperlink ref="O19" location="'Captures'!B1178" display="VIT-15 → ligne 1178"/>
-    <hyperlink ref="O21" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
-    <hyperlink ref="O24" location="'Captures'!B98" display="BLQ-JURIDIQUE → ligne 98"/>
-    <hyperlink ref="O32" location="'Captures'!B243" display="ACH-03 → ligne 243"/>
-    <hyperlink ref="O33" location="'Captures'!B277" display="ACH-04 → ligne 277&#10;BLQ-KYC → ligne 126"/>
-    <hyperlink ref="O34" location="'Captures'!B434" display="ADM-20 → ligne 434&#10;BLQ-KYC → ligne 126"/>
-    <hyperlink ref="O36" location="'Captures'!B126" display="BLQ-KYC → ligne 126"/>
-    <hyperlink ref="O39" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
-    <hyperlink ref="O41" location="'Captures'!B311" display="ACH-12 → ligne 311"/>
-    <hyperlink ref="O44" location="'Captures'!B613" display="APP-03 → ligne 613"/>
+    <hyperlink ref="O19" location="'Captures'!B1319" display="VIT-15 → ligne 1319"/>
+    <hyperlink ref="O24" location="'Captures'!B127" display="BLQ-JURIDIQUE → ligne 127"/>
+    <hyperlink ref="O32" location="'Captures'!B272" display="ACH-03 → ligne 272"/>
+    <hyperlink ref="O33" location="'Captures'!B306" display="ACH-04 → ligne 306&#10;ACH-04-wave → ligne 414&#10;ACH-04-carte → ligne 340&#10;ACH-04-prefill → ligne 378"/>
+    <hyperlink ref="O34" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66&#10;ADM-20 → ligne 575"/>
+    <hyperlink ref="O35" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66"/>
+    <hyperlink ref="O36" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66&#10;BLQ-KYC → ligne 155"/>
+    <hyperlink ref="O37" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66"/>
+    <hyperlink ref="O41" location="'Captures'!B452" display="ACH-12 → ligne 452"/>
+    <hyperlink ref="O44" location="'Captures'!B754" display="APP-03 → ligne 754"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId2"/>
-    <hyperlink ref="O46" location="'Captures'!B641" display="APP-05 → ligne 641"/>
+    <hyperlink ref="O46" location="'Captures'!B782" display="APP-05 → ligne 782"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId3"/>
-    <hyperlink ref="O48" location="'Captures'!B669" display="APP-07 → ligne 669&#10;APP-07-mobile → ligne 697"/>
-    <hyperlink ref="O59" location="'Captures'!B155" display="BLQ-VIDEOS → ligne 155"/>
-    <hyperlink ref="O62" location="'Captures'!B877" display="COL-01 → ligne 877"/>
-    <hyperlink ref="O64" location="'Captures'!B909" display="COL-03 → ligne 909"/>
-    <hyperlink ref="O66" location="'Captures'!B214" display="BLQ-ZOOM → ligne 214&#10;COL-05-seance-passee → ligne 937"/>
-    <hyperlink ref="O67" location="'Captures'!B877" display="COL-01 → ligne 877"/>
-    <hyperlink ref="O71" location="'Captures'!B1021" display="PRI-02 → ligne 1021&#10;PRI-02-admin → ligne 1049"/>
-    <hyperlink ref="O73" location="'Captures'!B1094" display="PRI-04 → ligne 1094"/>
-    <hyperlink ref="O82" location="'Captures'!B784" display="ATT-05 → ligne 784"/>
-    <hyperlink ref="O83" location="'Captures'!B849" display="ATT-07 → ligne 849"/>
-    <hyperlink ref="O84" location="'Captures'!B849" display="ATT-07 → ligne 849"/>
-    <hyperlink ref="O86" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
-    <hyperlink ref="O91" location="'Captures'!B965" display="FOR-05 → ligne 965&#10;FOR-05-releve → ligne 993"/>
-    <hyperlink ref="O99" location="'Captures'!B350" display="ADM-05 → ligne 350"/>
-    <hyperlink ref="O100" location="'Captures'!B378" display="ADM-06 → ligne 378"/>
-    <hyperlink ref="O101" location="'Captures'!B378" display="ADM-06 → ligne 378"/>
-    <hyperlink ref="O106" location="'Captures'!B406" display="ADM-12 → ligne 406"/>
-    <hyperlink ref="O108" location="'Captures'!B406" display="ADM-12 → ligne 406"/>
-    <hyperlink ref="O111" location="'Captures'!B66" display="BLQ-GA4 → ligne 66"/>
-    <hyperlink ref="O112" location="'Captures'!B66" display="BLQ-GA4 → ligne 66"/>
-    <hyperlink ref="O114" location="'Captures'!B434" display="ADM-20 → ligne 434&#10;ADM-20-editeur → ligne 515"/>
-    <hyperlink ref="O115" location="'Captures'!B543" display="ADM-21 → ligne 543"/>
-    <hyperlink ref="O116" location="'Captures'!B571" display="ADM-22 → ligne 571"/>
-    <hyperlink ref="O117" location="'Captures'!B571" display="ADM-22 → ligne 571"/>
-    <hyperlink ref="O118" location="'Captures'!B571" display="ADM-22 → ligne 571"/>
-    <hyperlink ref="O120" location="'Captures'!B311" display="ACH-12 → ligne 311"/>
-    <hyperlink ref="O128" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
+    <hyperlink ref="O48" location="'Captures'!B810" display="APP-07 → ligne 810&#10;APP-07-mobile → ligne 838"/>
+    <hyperlink ref="O59" location="'Captures'!B184" display="BLQ-VIDEOS → ligne 184"/>
+    <hyperlink ref="O62" location="'Captures'!B1018" display="COL-01 → ligne 1018"/>
+    <hyperlink ref="O64" location="'Captures'!B1050" display="COL-03 → ligne 1050"/>
+    <hyperlink ref="O66" location="'Captures'!B1078" display="COL-05-seance-passee → ligne 1078"/>
+    <hyperlink ref="O67" location="'Captures'!B1018" display="COL-01 → ligne 1018"/>
+    <hyperlink ref="O71" location="'Captures'!B1162" display="PRI-02 → ligne 1162&#10;PRI-02-admin → ligne 1190"/>
+    <hyperlink ref="O73" location="'Captures'!B1235" display="PRI-04 → ligne 1235"/>
+    <hyperlink ref="O82" location="'Captures'!B925" display="ATT-05 → ligne 925"/>
+    <hyperlink ref="O83" location="'Captures'!B990" display="ATT-07 → ligne 990"/>
+    <hyperlink ref="O84" location="'Captures'!B990" display="ATT-07 → ligne 990"/>
+    <hyperlink ref="O91" location="'Captures'!B1106" display="FOR-05 → ligne 1106&#10;FOR-05-releve → ligne 1134"/>
+    <hyperlink ref="O99" location="'Captures'!B491" display="ADM-05 → ligne 491"/>
+    <hyperlink ref="O100" location="'Captures'!B519" display="ADM-06 → ligne 519"/>
+    <hyperlink ref="O101" location="'Captures'!B519" display="ADM-06 → ligne 519"/>
+    <hyperlink ref="O106" location="'Captures'!B547" display="ADM-12 → ligne 547"/>
+    <hyperlink ref="O108" location="'Captures'!B547" display="ADM-12 → ligne 547"/>
+    <hyperlink ref="O111" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
+    <hyperlink ref="O112" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
+    <hyperlink ref="O114" location="'Captures'!B575" display="ADM-20 → ligne 575&#10;ADM-20-editeur → ligne 656"/>
+    <hyperlink ref="O115" location="'Captures'!B684" display="ADM-21 → ligne 684"/>
+    <hyperlink ref="O116" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
+    <hyperlink ref="O117" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
+    <hyperlink ref="O118" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
+    <hyperlink ref="O120" location="'Captures'!B452" display="ACH-12 → ligne 452"/>
     <hyperlink ref="O142" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
-    <hyperlink ref="O143" location="'Captures'!B66" display="BLQ-GA4 → ligne 66"/>
-    <hyperlink ref="O148" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
+    <hyperlink ref="O143" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
@@ -15806,7 +15430,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -18309,7 +17932,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -20170,7 +19792,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -20239,7 +19860,11 @@
           <t>Client + dev</t>
         </is>
       </c>
-      <c r="G5" s="33" t="n"/>
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 : https://emasterclass.bigfive.solutions/ (URL définitive)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
@@ -20272,7 +19897,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G6" s="33" t="n"/>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
@@ -20305,7 +19934,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G7" s="33" t="n"/>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>Vérifié le 15/10 (webhook joignable)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="42" t="inlineStr">
@@ -20338,7 +19971,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G8" s="33" t="n"/>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
@@ -20470,7 +20107,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G12" s="33" t="n"/>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
@@ -20503,7 +20144,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G13" s="33" t="n"/>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
@@ -20569,7 +20214,11 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="G15" s="33" t="n"/>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 (en-tête Bearer)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
@@ -20602,7 +20251,11 @@
           <t>Client + dev</t>
         </is>
       </c>
-      <c r="G16" s="33" t="n"/>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>Sans objet (la liste d’IP ne sert qu’aux reversements)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
@@ -20668,7 +20321,11 @@
           <t>Équipe</t>
         </is>
       </c>
-      <c r="G18" s="33" t="n"/>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 : Orange 200 F et MTN 200 F réussis, modules ouverts</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
@@ -20701,7 +20358,11 @@
           <t>Équipe</t>
         </is>
       </c>
-      <c r="G19" s="33" t="n"/>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 : refus MTN « solde ou plafond » affiché et tracé</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="42" t="inlineStr">
@@ -20734,7 +20395,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G20" s="33" t="n"/>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>15/10 : échec MTN reçu et tracé par le webhook</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
@@ -20800,7 +20465,11 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="G22" s="33" t="n"/>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>À faire : rembourser les 2 paiements de 200 F, remettre les prix</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
@@ -20868,7 +20537,7 @@
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>Créée — désactivée (15/10)</t>
+          <t>Fait le 15/10 (activée)</t>
         </is>
       </c>
     </row>
@@ -20905,7 +20574,7 @@
       </c>
       <c r="G25" s="33" t="inlineStr">
         <is>
-          <t>Client ID manquant (15/10)</t>
+          <t>Fait le 15/10</t>
         </is>
       </c>
     </row>
@@ -20940,7 +20609,11 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="G26" s="33" t="n"/>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
@@ -20973,7 +20646,11 @@
           <t>Admin</t>
         </is>
       </c>
-      <c r="G27" s="33" t="n"/>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 (ses-008 fictive annulée)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
@@ -21006,7 +20683,11 @@
           <t>Équipe</t>
         </is>
       </c>
-      <c r="G28" s="33" t="n"/>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 : ses-010 → réunion 83441083225 chez Zoom</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
@@ -21140,7 +20821,6 @@
       </c>
       <c r="G32" s="33" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="45" customHeight="1" s="31">
       <c r="A34" s="43" t="inlineStr">
         <is>
@@ -21148,7 +20828,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="58" t="inlineStr">
         <is>
@@ -21398,7 +21077,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -22714,7 +22392,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -24355,7 +24032,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -24591,7 +24267,6 @@
       </c>
       <c r="E12" s="33" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14" ht="31.5" customHeight="1" s="31">
       <c r="A14" s="4" t="inlineStr">
         <is>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -531,9 +531,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -559,9 +556,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -587,9 +581,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -615,9 +606,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -643,9 +631,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -671,9 +656,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -699,9 +681,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -727,9 +706,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -755,9 +731,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -783,9 +756,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -811,9 +781,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -839,9 +806,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -867,9 +831,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -895,9 +856,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -923,9 +881,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -951,9 +906,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -979,9 +931,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -993,7 +942,7 @@
       <row>576</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="14601825"/>
+    <ext cx="7239000" cy="4219575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -1007,9 +956,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1018,10 +964,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>657</row>
+      <row>603</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="14601825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -1035,9 +981,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1046,7 +989,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>685</row>
+      <row>684</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1063,9 +1006,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1074,10 +1014,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>713</row>
+      <row>712</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="7115175"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -1091,9 +1031,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1102,10 +1039,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>755</row>
+      <row>740</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="7115175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -1119,9 +1056,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1130,7 +1064,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>783</row>
+      <row>782</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1147,9 +1081,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1158,7 +1089,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>811</row>
+      <row>810</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1175,9 +1106,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1186,10 +1114,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>839</row>
+      <row>838</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="15668625"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -1203,9 +1131,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1214,10 +1139,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>926</row>
+      <row>866</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="11601450"/>
+    <ext cx="7239000" cy="15668625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -1231,9 +1156,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1242,10 +1164,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>991</row>
+      <row>953</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="11601450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -1259,9 +1181,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1270,10 +1189,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1019</row>
+      <row>1018</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="5267325"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -1287,9 +1206,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1298,10 +1214,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1051</row>
+      <row>1046</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="5267325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1315,9 +1231,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1326,7 +1239,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1079</row>
+      <row>1078</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1343,9 +1256,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1354,10 +1264,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1107</row>
+      <row>1106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="4981575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -1371,9 +1281,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1382,7 +1289,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1135</row>
+      <row>1137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1399,9 +1306,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1410,7 +1314,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1163</row>
+      <row>1165</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1427,9 +1331,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1438,10 +1339,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1191</row>
+      <row>1193</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="7724775"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1455,9 +1356,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1466,7 +1364,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1236</row>
+      <row>1221</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1483,9 +1381,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1494,10 +1389,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1264</row>
+      <row>1249</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7239000" cy="4524375"/>
+    <ext cx="7239000" cy="7724775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1511,9 +1406,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1522,7 +1414,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1292</row>
+      <row>1294</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1539,9 +1431,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1550,7 +1439,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1320</row>
+      <row>1322</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7239000" cy="4524375"/>
@@ -1567,9 +1456,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1578,10 +1464,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1348</row>
+      <row>1350</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11430000" cy="6667500"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1595,9 +1481,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1606,10 +1489,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1376</row>
+      <row>1378</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11430000" cy="7877175"/>
+    <ext cx="7239000" cy="4524375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1623,9 +1506,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1924,6 +1804,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -2328,7 +2209,7 @@
     <row r="44" ht="27.75" customHeight="1" s="31">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>• Mot de passe de démonstration commun encore actif sur 6 comptes sur 7 ; retiré du README le 15/10, script de renouvellement prêt (D2).</t>
+          <t>• Mot de passe de démonstration commun encore actif sur tous les comptes et écrit dans le README.</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2230,14 @@
     <row r="47" ht="27.75" customHeight="1" s="31">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>• /admin/apprenants : l'erreur 500 du 15/10 est corrigée (27d835b) et vérifiée ; reste à rejouer la création d'un apprenant (ADM-12).</t>
+          <t>• /admin/apprenants plante (erreur 500) depuis le 15/10 : création et export d'apprenants indisponibles — reste dev (D1).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="27.75" customHeight="1" s="31">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration : lancer npm run auth:renouveler -- --appliquer (D2).</t>
+          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié — à changer immédiatement (D2).</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B1376"/>
+  <dimension ref="A1:B1378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -3456,6 +3337,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="59" t="inlineStr">
         <is>
@@ -3470,6 +3352,37 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="59" t="inlineStr">
         <is>
@@ -3484,6 +3397,33 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
     <row r="66">
       <c r="B66" s="59" t="inlineStr">
         <is>
@@ -3498,6 +3438,33 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
     <row r="95">
       <c r="B95" s="59" t="inlineStr">
         <is>
@@ -3512,6 +3479,36 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
     <row r="127">
       <c r="B127" s="59" t="inlineStr">
         <is>
@@ -3526,6 +3523,32 @@
         </is>
       </c>
     </row>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
     <row r="155">
       <c r="B155" s="59" t="inlineStr">
         <is>
@@ -3540,6 +3563,33 @@
         </is>
       </c>
     </row>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
     <row r="184">
       <c r="B184" s="59" t="inlineStr">
         <is>
@@ -3554,6 +3604,63 @@
         </is>
       </c>
     </row>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
     <row r="243">
       <c r="B243" s="59" t="inlineStr">
         <is>
@@ -3561,6 +3668,34 @@
         </is>
       </c>
     </row>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
     <row r="272">
       <c r="B272" s="59" t="inlineStr">
         <is>
@@ -3575,6 +3710,38 @@
         </is>
       </c>
     </row>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
     <row r="306">
       <c r="B306" s="59" t="inlineStr">
         <is>
@@ -3589,6 +3756,38 @@
         </is>
       </c>
     </row>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
     <row r="340">
       <c r="B340" s="59" t="inlineStr">
         <is>
@@ -3603,6 +3802,42 @@
         </is>
       </c>
     </row>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
     <row r="378">
       <c r="B378" s="59" t="inlineStr">
         <is>
@@ -3617,6 +3852,40 @@
         </is>
       </c>
     </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
     <row r="414">
       <c r="B414" s="59" t="inlineStr">
         <is>
@@ -3631,6 +3900,42 @@
         </is>
       </c>
     </row>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
     <row r="452">
       <c r="B452" s="59" t="inlineStr">
         <is>
@@ -3645,6 +3950,43 @@
         </is>
       </c>
     </row>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
     <row r="491">
       <c r="B491" s="59" t="inlineStr">
         <is>
@@ -3659,6 +4001,32 @@
         </is>
       </c>
     </row>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
     <row r="519">
       <c r="B519" s="59" t="inlineStr">
         <is>
@@ -3673,339 +4041,1137 @@
         </is>
       </c>
     </row>
-    <row r="547" s="31">
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547">
       <c r="B547" s="59" t="inlineStr">
         <is>
           <t>ADM-12 — /admin/apprenants : erreur 500 constatée le 15/10 (reste dev)</t>
         </is>
       </c>
     </row>
-    <row r="548" s="31">
+    <row r="548">
       <c r="B548" s="60" t="inlineStr">
         <is>
-          <t>Cas : ADM-12, ADM-14</t>
-        </is>
-      </c>
-    </row>
+          <t>Cas : ADM-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
     <row r="575">
       <c r="B575" s="59" t="inlineStr">
         <is>
+          <t>ADM-12-corrige — capture complémentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602">
+      <c r="B602" s="59" t="inlineStr">
+        <is>
           <t>ADM-20 — Transactions (admin supérieur) : les essais Visa / Djamo restent « En attente »</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="B576" s="60" t="inlineStr">
+    <row r="603">
+      <c r="B603" s="60" t="inlineStr">
         <is>
           <t>Cas : ACH-05, ADM-20</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="B656" s="59" t="inlineStr">
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683">
+      <c r="B683" s="59" t="inlineStr">
         <is>
           <t>ADM-20-editeur — ADM-20 : OK</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="B657" s="60" t="inlineStr">
+    <row r="684">
+      <c r="B684" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-20</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="B684" s="59" t="inlineStr">
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711">
+      <c r="B711" s="59" t="inlineStr">
         <is>
           <t>ADM-21 — ADM-21 : OK</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="B685" s="60" t="inlineStr">
+    <row r="712">
+      <c r="B712" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-21</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="B712" s="59" t="inlineStr">
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739">
+      <c r="B739" s="59" t="inlineStr">
         <is>
           <t>ADM-22 — ADM-22 : OK · ADM-23 : OK · ADM-24 : OK</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="B713" s="60" t="inlineStr">
+    <row r="740">
+      <c r="B740" s="60" t="inlineStr">
         <is>
           <t>Cas : ADM-22, ADM-23, ADM-24</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="B754" s="59" t="inlineStr">
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781">
+      <c r="B781" s="59" t="inlineStr">
         <is>
           <t>APP-03 — APP-03 : OK</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="B755" s="60" t="inlineStr">
+    <row r="782">
+      <c r="B782" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-03</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="B782" s="59" t="inlineStr">
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809">
+      <c r="B809" s="59" t="inlineStr">
         <is>
           <t>APP-05 — APP-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="B783" s="60" t="inlineStr">
+    <row r="810">
+      <c r="B810" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-05</t>
         </is>
       </c>
     </row>
-    <row r="810">
-      <c r="B810" s="59" t="inlineStr">
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837">
+      <c r="B837" s="59" t="inlineStr">
         <is>
           <t>APP-07 — APP-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="811">
-      <c r="B811" s="60" t="inlineStr">
+    <row r="838">
+      <c r="B838" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-07</t>
         </is>
       </c>
     </row>
-    <row r="838">
-      <c r="B838" s="59" t="inlineStr">
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865">
+      <c r="B865" s="59" t="inlineStr">
         <is>
           <t>APP-07-mobile — APP-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="839">
-      <c r="B839" s="60" t="inlineStr">
+    <row r="866">
+      <c r="B866" s="60" t="inlineStr">
         <is>
           <t>Cas : APP-07</t>
         </is>
       </c>
     </row>
-    <row r="925">
-      <c r="B925" s="59" t="inlineStr">
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952">
+      <c r="B952" s="59" t="inlineStr">
         <is>
           <t>ATT-05 — ATT-05 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="926">
-      <c r="B926" s="60" t="inlineStr">
+    <row r="953">
+      <c r="B953" s="60" t="inlineStr">
         <is>
           <t>Cas : ATT-05</t>
         </is>
       </c>
     </row>
-    <row r="990">
-      <c r="B990" s="59" t="inlineStr">
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017">
+      <c r="B1017" s="59" t="inlineStr">
         <is>
           <t>ATT-07 — ATT-06 : OK · ATT-07 : OK</t>
         </is>
       </c>
     </row>
-    <row r="991">
-      <c r="B991" s="60" t="inlineStr">
+    <row r="1018">
+      <c r="B1018" s="60" t="inlineStr">
         <is>
           <t>Cas : ATT-06, ATT-07</t>
         </is>
       </c>
     </row>
-    <row r="1018">
-      <c r="B1018" s="59" t="inlineStr">
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045">
+      <c r="B1045" s="59" t="inlineStr">
         <is>
           <t>COL-01 — COL-01 : OK · COL-06 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1019">
-      <c r="B1019" s="60" t="inlineStr">
+    <row r="1046">
+      <c r="B1046" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-01, COL-06</t>
         </is>
       </c>
     </row>
-    <row r="1050">
-      <c r="B1050" s="59" t="inlineStr">
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077">
+      <c r="B1077" s="59" t="inlineStr">
         <is>
           <t>COL-03 — COL-03 : À retester</t>
         </is>
       </c>
     </row>
-    <row r="1051">
-      <c r="B1051" s="60" t="inlineStr">
+    <row r="1078">
+      <c r="B1078" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-03</t>
         </is>
       </c>
     </row>
-    <row r="1078">
-      <c r="B1078" s="59" t="inlineStr">
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105">
+      <c r="B1105" s="59" t="inlineStr">
+        <is>
+          <t>COL-05-corrige — capture complémentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136">
+      <c r="B1136" s="59" t="inlineStr">
         <is>
           <t>COL-05-seance-passee — Séance du 19/09 affichée « EN DIRECT · 621 h » (reste dev)</t>
         </is>
       </c>
     </row>
-    <row r="1079">
-      <c r="B1079" s="60" t="inlineStr">
+    <row r="1137">
+      <c r="B1137" s="60" t="inlineStr">
         <is>
           <t>Cas : COL-05</t>
         </is>
       </c>
     </row>
-    <row r="1106">
-      <c r="B1106" s="59" t="inlineStr">
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164">
+      <c r="B1164" s="59" t="inlineStr">
         <is>
           <t>FOR-05 — FOR-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1107">
-      <c r="B1107" s="60" t="inlineStr">
+    <row r="1165">
+      <c r="B1165" s="60" t="inlineStr">
         <is>
           <t>Cas : FOR-05</t>
         </is>
       </c>
     </row>
-    <row r="1134">
-      <c r="B1134" s="59" t="inlineStr">
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192">
+      <c r="B1192" s="59" t="inlineStr">
         <is>
           <t>FOR-05-releve — FOR-05 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1135">
-      <c r="B1135" s="60" t="inlineStr">
+    <row r="1193">
+      <c r="B1193" s="60" t="inlineStr">
         <is>
           <t>Cas : FOR-05</t>
         </is>
       </c>
     </row>
-    <row r="1162">
-      <c r="B1162" s="59" t="inlineStr">
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220">
+      <c r="B1220" s="59" t="inlineStr">
         <is>
           <t>PRI-02 — PRI-02 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1163">
-      <c r="B1163" s="60" t="inlineStr">
+    <row r="1221">
+      <c r="B1221" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-02</t>
         </is>
       </c>
     </row>
-    <row r="1190">
-      <c r="B1190" s="59" t="inlineStr">
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248">
+      <c r="B1248" s="59" t="inlineStr">
         <is>
           <t>PRI-02-admin — PRI-02 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1191">
-      <c r="B1191" s="60" t="inlineStr">
+    <row r="1249">
+      <c r="B1249" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-02</t>
         </is>
       </c>
     </row>
-    <row r="1235">
-      <c r="B1235" s="59" t="inlineStr">
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293">
+      <c r="B1293" s="59" t="inlineStr">
         <is>
           <t>PRI-04 — PRI-04 : Pas un bug</t>
         </is>
       </c>
     </row>
-    <row r="1236">
-      <c r="B1236" s="60" t="inlineStr">
+    <row r="1294">
+      <c r="B1294" s="60" t="inlineStr">
         <is>
           <t>Cas : PRI-04</t>
         </is>
       </c>
     </row>
-    <row r="1263">
-      <c r="B1263" s="59" t="inlineStr">
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321">
+      <c r="B1321" s="59" t="inlineStr">
         <is>
           <t>VIT-11-accueil — VIT-11 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1264">
-      <c r="B1264" s="60" t="inlineStr">
+    <row r="1322">
+      <c r="B1322" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-11</t>
         </is>
       </c>
     </row>
-    <row r="1291">
-      <c r="B1291" s="59" t="inlineStr">
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349">
+      <c r="B1349" s="59" t="inlineStr">
         <is>
           <t>VIT-12-fiche — VIT-12 : OK</t>
         </is>
       </c>
     </row>
-    <row r="1292">
-      <c r="B1292" s="60" t="inlineStr">
+    <row r="1350">
+      <c r="B1350" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-12</t>
         </is>
       </c>
     </row>
-    <row r="1319">
-      <c r="B1319" s="59" t="inlineStr">
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377">
+      <c r="B1377" s="59" t="inlineStr">
         <is>
           <t>VIT-15 — VIT-15 : Bloqué — client</t>
         </is>
       </c>
     </row>
-    <row r="1320">
-      <c r="B1320" s="60" t="inlineStr">
+    <row r="1378">
+      <c r="B1378" s="60" t="inlineStr">
         <is>
           <t>Cas : VIT-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="1347">
-      <c r="B1347" s="59" t="inlineStr">
-        <is>
-          <t>ADM-12-corrige — /admin/apprenants s'affiche de nouveau (corrigé le 15/10, 27d835b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1348">
-      <c r="B1348" s="60" t="inlineStr">
-        <is>
-          <t>Cas : ADM-12, ADM-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="1375">
-      <c r="B1375" s="59" t="inlineStr">
-        <is>
-          <t>COL-05-corrige — Séance du 19/09 affichée « TERMINÉE · 19 septembre à 20:00 » (corrigé le 15/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1376">
-      <c r="B1376" s="60" t="inlineStr">
-        <is>
-          <t>Cas : COL-05</t>
         </is>
       </c>
     </row>
@@ -4049,6 +5215,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -4137,7 +5304,7 @@
       <c r="H6" s="51" t="inlineStr">
         <is>
           <t>BLQ-KYC → Captures, ligne 155
-ADM-20 → Captures, ligne 575</t>
+ADM-20 → Captures, ligne 602</t>
         </is>
       </c>
     </row>
@@ -4433,7 +5600,7 @@
       </c>
       <c r="H13" s="51" t="inlineStr">
         <is>
-          <t>ATT-05 → Captures, ligne 925</t>
+          <t>ATT-05 → Captures, ligne 952</t>
         </is>
       </c>
     </row>
@@ -4475,7 +5642,7 @@
       </c>
       <c r="H14" s="51" t="inlineStr">
         <is>
-          <t>VIT-15 → Captures, ligne 1319</t>
+          <t>VIT-15 → Captures, ligne 1377</t>
         </is>
       </c>
     </row>
@@ -4518,7 +5685,7 @@
       <c r="H15" s="51" t="inlineStr">
         <is>
           <t>BLQ-GA4 → Captures, ligne 95
-ADM-21 → Captures, ligne 684</t>
+ADM-21 → Captures, ligne 711</t>
         </is>
       </c>
     </row>
@@ -4690,6 +5857,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
         <is>
@@ -4747,12 +5916,12 @@
       </c>
       <c r="B24" s="49" t="inlineStr">
         <is>
-          <t>/admin/apprenants plante (erreur 500)</t>
+          <t>/admin/apprenants répondait une erreur 500</t>
         </is>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>Corrigé (27d835b)</t>
+          <t>Corrigé</t>
         </is>
       </c>
       <c r="D24" s="50" t="inlineStr">
@@ -4762,7 +5931,7 @@
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>« Cannot read properties of undefined (reading 'length') », app/pages/admin/apprenants.vue:502. Cause : une fusion a gardé l'API qui renvoie { apprenants, choix } et repris un écran qui attend une simple liste ; l'écran parcourait l'objet au lieu des apprenants. L'écran lit désormais la liste.</t>
+          <t>La page s'affiche de nouveau sans erreur (vérifié le 15/10 sur la base en ligne).</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
@@ -4772,13 +5941,12 @@
       </c>
       <c r="G24" s="50" t="inlineStr">
         <is>
-          <t>Vérifié le 15/10 sur la base en ligne : liste des 10 comptes, fiche, historique, export CSV (10 lignes, 13 colonnes), formulaire Prénom / Nom. Reste au testeur : créer un apprenant de test (ADM-12), non rejoué pour ne rien écrire en base.</t>
+          <t>Rejouer la création et l’export.</t>
         </is>
       </c>
       <c r="H24" s="51" t="inlineStr">
         <is>
-          <t>ADM-12 → Captures, ligne 547
-ADM-12-corrige → Captures, ligne 1347</t>
+          <t>ADM-12 → Captures, ligne 547</t>
         </is>
       </c>
     </row>
@@ -4790,12 +5958,12 @@
       </c>
       <c r="B25" s="49" t="inlineStr">
         <is>
-          <t>Mots de passe de démonstration encore actifs (dont l'administrateur principal)</t>
+          <t>Mot de passe de démonstration encore actif sur un administrateur principal</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>Big Five (lancer le script)</t>
+          <t>Développement + Big Five</t>
         </is>
       </c>
       <c r="D25" s="50" t="inlineStr">
@@ -4805,7 +5973,7 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>Lecture du 15/10 sur la base en ligne : 6 comptes sur 7 acceptent encore le mot de passe commun du jeu de données — cossi@, jeremie.declercq@, houefa@bigfiveabidjan.com, editeur@bigfive.ci, formateur@bigfive.ci, aya@example.ci. Seul jeanluc@ l'a changé.</t>
+          <t>cossi@bigfiveabidjan.com s'ouvre avec le mot de passe publié dans le README.</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -4815,7 +5983,7 @@
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>Mot de passe retiré du README et du TODO le 15/10. Script prêt : npm run auth:renouveler (lecture seule) puis npm run auth:renouveler -- --appliquer, qui tire un mot de passe aléatoire par compte et l'affiche une seule fois dans le terminal : le reporter dans un gestionnaire, le transmettre à son titulaire. Puis remplacer NUXT_SESSION_PASSWORD sur Vercel pour fermer les sessions ouvertes.</t>
+          <t>Retiré du README le 15/10. Reste à changer le mot de passe de cossi@ et des autres comptes du jeu de données.</t>
         </is>
       </c>
       <c r="H25" s="50" t="inlineStr">
@@ -4837,7 +6005,7 @@
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>Corrigé (27d835b)</t>
+          <t>Corrigé (dans main)</t>
         </is>
       </c>
       <c r="D26" s="50" t="inlineStr">
@@ -4857,13 +6025,12 @@
       </c>
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>Vérifié le 15/10 : la séance du 19/09 affiche « TERMINÉE · 19 septembre à 20:00 » et « Cette séance s'est terminée », bouton d'entrée grisé, y compris pour le formateur et l'administrateur (retouche du bouton à commiter).</t>
+          <t>Corrigé : une séance passée affiche « Terminée ».</t>
         </is>
       </c>
       <c r="H26" s="51" t="inlineStr">
         <is>
-          <t>COL-05-seance-passee → Captures, ligne 1078
-COL-05-corrige → Captures, ligne 1375</t>
+          <t>COL-05-seance-passee → Captures, ligne 1136</t>
         </is>
       </c>
     </row>
@@ -4922,7 +6089,7 @@
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Développé (2bc3bcc)</t>
         </is>
       </c>
       <c r="D28" s="50" t="inlineStr">
@@ -4932,7 +6099,7 @@
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>Aucune tâche ne relit les commandes restées « En attente ».</t>
+          <t>Tâche quotidienne qui relit le statut FeexPay des commandes restées en attente.</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
@@ -4942,12 +6109,12 @@
       </c>
       <c r="G28" s="50" t="inlineStr">
         <is>
-          <t>Tâche planifiée de rapprochement.</t>
+          <t>Vérifier après déploiement.</t>
         </is>
       </c>
       <c r="H28" s="51" t="inlineStr">
         <is>
-          <t>ADM-20 → Captures, ligne 575</t>
+          <t>ADM-20 → Captures, ligne 602</t>
         </is>
       </c>
     </row>
@@ -4964,7 +6131,7 @@
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Développé (2bc3bcc)</t>
         </is>
       </c>
       <c r="D29" s="50" t="inlineStr">
@@ -4974,7 +6141,7 @@
       </c>
       <c r="E29" s="50" t="inlineStr">
         <is>
-          <t>Ces paiements ne sont suivis que dans la console FeexPay.</t>
+          <t>Les paiements de séance deviennent des transactions.</t>
         </is>
       </c>
       <c r="F29" s="50" t="inlineStr">
@@ -4984,7 +6151,7 @@
       </c>
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>Les faire apparaître dans Transactions.</t>
+          <t>Exécuter la migration 38 sur la base hébergée avant de déployer.</t>
         </is>
       </c>
       <c r="H29" s="50" t="inlineStr">
@@ -5006,7 +6173,7 @@
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Corrigé (2bc3bcc)</t>
         </is>
       </c>
       <c r="D30" s="50" t="inlineStr">
@@ -5016,7 +6183,7 @@
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>npm run typecheck : 5 erreurs sur Referentiels.vue (sans effet sur le build).</t>
+          <t>npm run typecheck : 0 erreur.</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
@@ -5026,7 +6193,7 @@
       </c>
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>Corriger le typage.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="50" t="inlineStr">
@@ -5048,7 +6215,7 @@
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>Développement</t>
+          <t>Développé (2bc3bcc)</t>
         </is>
       </c>
       <c r="D31" s="50" t="inlineStr">
@@ -5058,7 +6225,7 @@
       </c>
       <c r="E31" s="50" t="inlineStr">
         <is>
-          <t>visionnages et reglages_attestation répondent 200 (vide) au lieu de 401.</t>
+          <t>Migration 37 : droits retirés sur toutes les tables.</t>
         </is>
       </c>
       <c r="F31" s="50" t="inlineStr">
@@ -5068,7 +6235,7 @@
       </c>
       <c r="G31" s="50" t="inlineStr">
         <is>
-          <t>Retirer le droit, comme sur les 43 autres tables.</t>
+          <t>Exécuter la migration 37 sur la base hébergée.</t>
         </is>
       </c>
       <c r="H31" s="50" t="inlineStr">
@@ -5090,7 +6257,7 @@
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>Développé, à fusionner</t>
+          <t>Fusionné dans main</t>
         </is>
       </c>
       <c r="D32" s="50" t="inlineStr">
@@ -5100,7 +6267,7 @@
       </c>
       <c r="E32" s="50" t="inlineStr">
         <is>
-          <t>Les deux modèles sont écrits (commit 5b98316, branche jl/practical-chatelet-e7dbbe) ; ils ne sont pas encore dans main.</t>
+          <t>Les deux modèles sont écrits et fusionnés (5b98316, a06e132).</t>
         </is>
       </c>
       <c r="F32" s="50" t="inlineStr">
@@ -5110,7 +6277,7 @@
       </c>
       <c r="G32" s="50" t="inlineStr">
         <is>
-          <t>Fusionner la branche dans main, déployer, puis vérifier les deux e-mails sur un vrai achat et une vraie délivrance.</t>
+          <t>Déployer, puis vérifier les deux e-mails sur un vrai achat et une vraie délivrance.</t>
         </is>
       </c>
       <c r="H32" s="50" t="inlineStr">
@@ -5119,6 +6286,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
         <is>
@@ -5468,17 +6637,17 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H6" location="'Captures'!B155" display="BLQ-KYC → Captures, ligne 155&#10;ADM-20 → Captures, ligne 575"/>
+    <hyperlink ref="H6" location="'Captures'!B155" display="BLQ-KYC → Captures, ligne 155&#10;ADM-20 → Captures, ligne 602"/>
     <hyperlink ref="H10" location="'Captures'!B127" display="BLQ-JURIDIQUE → Captures, ligne 127&#10;ACH-03 → Captures, ligne 272"/>
     <hyperlink ref="H11" location="'Captures'!B184" display="BLQ-VIDEOS → Captures, ligne 184"/>
     <hyperlink ref="H12" location="'Captures'!B4" display="BLQ-CATALOGUE → Captures, ligne 4&#10;ADM-06 → Captures, ligne 519"/>
-    <hyperlink ref="H13" location="'Captures'!B925" display="ATT-05 → Captures, ligne 925"/>
-    <hyperlink ref="H14" location="'Captures'!B1319" display="VIT-15 → Captures, ligne 1319"/>
-    <hyperlink ref="H15" location="'Captures'!B95" display="BLQ-GA4 → Captures, ligne 95&#10;ADM-21 → Captures, ligne 684"/>
+    <hyperlink ref="H13" location="'Captures'!B952" display="ATT-05 → Captures, ligne 952"/>
+    <hyperlink ref="H14" location="'Captures'!B1377" display="VIT-15 → Captures, ligne 1377"/>
+    <hyperlink ref="H15" location="'Captures'!B95" display="BLQ-GA4 → Captures, ligne 95&#10;ADM-21 → Captures, ligne 711"/>
     <hyperlink ref="H17" location="'Captures'!B66" display="BLQ-FEEXPAY → Captures, ligne 66"/>
     <hyperlink ref="H24" location="'Captures'!B547" display="ADM-12 → Captures, ligne 547"/>
-    <hyperlink ref="H26" location="'Captures'!B1078" display="COL-05-seance-passee → Captures, ligne 1078"/>
-    <hyperlink ref="H28" location="'Captures'!B575" display="ADM-20 → Captures, ligne 575"/>
+    <hyperlink ref="H26" location="'Captures'!B1136" display="COL-05-seance-passee → Captures, ligne 1136"/>
+    <hyperlink ref="H28" location="'Captures'!B602" display="ADM-20 → Captures, ligne 602"/>
     <hyperlink ref="H39" location="'Captures'!B378" display="ACH-04-prefill → Captures, ligne 378"/>
     <hyperlink ref="H43" location="'Captures'!B414" display="ACH-04-wave → Captures, ligne 414&#10;ACH-04-carte → Captures, ligne 340"/>
   </hyperlinks>
@@ -5526,6 +6695,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -6206,7 +7376,7 @@
       </c>
       <c r="O15" s="53" t="inlineStr">
         <is>
-          <t>VIT-11-accueil → ligne 1263
+          <t>VIT-11-accueil → ligne 1321
 BLQ-CATALOGUE → ligne 4</t>
         </is>
       </c>
@@ -6272,7 +7442,7 @@
       </c>
       <c r="O16" s="53" t="inlineStr">
         <is>
-          <t>VIT-12-fiche → ligne 1291</t>
+          <t>VIT-12-fiche → ligne 1349</t>
         </is>
       </c>
     </row>
@@ -6456,7 +7626,7 @@
       </c>
       <c r="O19" s="53" t="inlineStr">
         <is>
-          <t>VIT-15 → ligne 1319</t>
+          <t>VIT-15 → ligne 1377</t>
         </is>
       </c>
     </row>
@@ -7351,7 +8521,7 @@
       <c r="O34" s="53" t="inlineStr">
         <is>
           <t>BLQ-FEEXPAY → ligne 66
-ADM-20 → ligne 575</t>
+ADM-20 → ligne 602</t>
         </is>
       </c>
     </row>
@@ -7620,8 +8790,16 @@
           <t>Toujours à faire : aucune tâche planifiée ne relit les commandes restées « en attente » (19 dans la base au 15/10). Seule la vérification commande par commande existe.</t>
         </is>
       </c>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
+      <c r="M38" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
+        </is>
+      </c>
+      <c r="N38" s="33" t="inlineStr">
+        <is>
+          <t>Développé le 15/10 : relance quotidienne des commandes restées en attente (cron Vercel 04:00, /api/taches/commandes), qui relit leur statut chez FeexPay. À vérifier après déploiement.</t>
+        </is>
+      </c>
       <c r="O38" s="33" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="31">
@@ -7680,7 +8858,7 @@
       </c>
       <c r="N39" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10 (commit 5b98316, branche jl/practical-chatelet-e7dbbe) : e-mail de confirmation d'achat avec module ou séance, montant, moyen et référence, envoyé une seule fois par commande. Pas encore fusionné dans main ni déployé : à retester en ligne après fusion, avec un vrai paiement.</t>
+          <t>Développé le 15/10 (commit 5b98316, fusionné dans main) : e-mail de confirmation d'achat avec module ou séance, montant, moyen et référence, envoyé une seule fois par commande. À retester en ligne après déploiement, avec un vrai paiement.</t>
         </is>
       </c>
       <c r="O39" s="33" t="n"/>
@@ -7994,7 +9172,7 @@
       </c>
       <c r="O44" s="53" t="inlineStr">
         <is>
-          <t>APP-03 → ligne 754</t>
+          <t>APP-03 → ligne 781</t>
         </is>
       </c>
     </row>
@@ -8125,7 +9303,7 @@
       </c>
       <c r="O46" s="53" t="inlineStr">
         <is>
-          <t>APP-05 → ligne 782</t>
+          <t>APP-05 → ligne 809</t>
         </is>
       </c>
     </row>
@@ -8256,8 +9434,8 @@
       </c>
       <c r="O48" s="53" t="inlineStr">
         <is>
-          <t>APP-07 → ligne 810
-APP-07-mobile → ligne 838</t>
+          <t>APP-07 → ligne 837
+APP-07-mobile → ligne 865</t>
         </is>
       </c>
     </row>
@@ -9087,7 +10265,7 @@
       </c>
       <c r="O62" s="53" t="inlineStr">
         <is>
-          <t>COL-01 → ligne 1018</t>
+          <t>COL-01 → ligne 1045</t>
         </is>
       </c>
     </row>
@@ -9217,7 +10395,7 @@
       </c>
       <c r="O64" s="53" t="inlineStr">
         <is>
-          <t>COL-03 → ligne 1050</t>
+          <t>COL-03 → ligne 1077</t>
         </is>
       </c>
     </row>
@@ -9334,12 +10512,12 @@
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>Zoom en réel depuis le 15/10. Création automatique validée : la session ses-010 créée depuis le site à 19:53 a reçu la réunion 83441083225, présente chez Zoom sous le compte cossi@bigfiveabidjan.com (2 h, salle d'attente). Restent à dérouler : entrée formateur et apprenant depuis la plateforme, report et annulation d'une réunion réelle. Une séance passée s'affichait « EN DIRECT · 621 h » : corrigé (27d835b) et vérifié le 15/10, elle affiche « TERMINÉE · 19 septembre à 20:00 ».</t>
+          <t>Zoom en réel depuis le 15/10. Création automatique validée : la session ses-010 créée depuis le site à 19:53 a reçu la réunion 83441083225, présente chez Zoom sous le compte cossi@bigfiveabidjan.com (2 h, salle d'attente). Restent à dérouler : entrée formateur et apprenant depuis la plateforme, report et annulation d'une réunion réelle. Une séance passée s'affichait « EN DIRECT » : corrigé.</t>
         </is>
       </c>
       <c r="O66" s="53" t="inlineStr">
         <is>
-          <t>COL-05-seance-passee → ligne 1078 · COL-05-corrige → ligne 1375</t>
+          <t>COL-05-seance-passee → ligne 1136</t>
         </is>
       </c>
     </row>
@@ -9404,7 +10582,7 @@
       </c>
       <c r="O67" s="53" t="inlineStr">
         <is>
-          <t>COL-01 → ligne 1018</t>
+          <t>COL-01 → ligne 1045</t>
         </is>
       </c>
     </row>
@@ -9640,8 +10818,8 @@
       </c>
       <c r="O71" s="53" t="inlineStr">
         <is>
-          <t>PRI-02 → ligne 1162
-PRI-02-admin → ligne 1190</t>
+          <t>PRI-02 → ligne 1220
+PRI-02-admin → ligne 1248</t>
         </is>
       </c>
     </row>
@@ -9771,7 +10949,7 @@
       </c>
       <c r="O73" s="53" t="inlineStr">
         <is>
-          <t>PRI-04 → ligne 1235</t>
+          <t>PRI-04 → ligne 1293</t>
         </is>
       </c>
     </row>
@@ -9991,8 +11169,16 @@
           <t>Le coaching privé passe par le même tunnel FeexPay que les modules ; dépend des clés live. Ces paiements ne créent pas de ligne dans /admin/transactions.</t>
         </is>
       </c>
-      <c r="M77" s="33" t="n"/>
-      <c r="N77" s="33" t="n"/>
+      <c r="M77" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
+        </is>
+      </c>
+      <c r="N77" s="33" t="inlineStr">
+        <is>
+          <t>Le paiement d'une séance de coaching privé devient une transaction visible dans /admin/transactions et les revenus. Exige la migration 38 sur la base hébergée (pas encore exécutée au 15/10 au soir).</t>
+        </is>
+      </c>
       <c r="O77" s="33" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="31">
@@ -10276,7 +11462,7 @@
       </c>
       <c r="O82" s="53" t="inlineStr">
         <is>
-          <t>ATT-05 → ligne 925</t>
+          <t>ATT-05 → ligne 952</t>
         </is>
       </c>
     </row>
@@ -10353,7 +11539,7 @@
       </c>
       <c r="O83" s="53" t="inlineStr">
         <is>
-          <t>ATT-07 → ligne 990</t>
+          <t>ATT-07 → ligne 1017</t>
         </is>
       </c>
     </row>
@@ -10426,7 +11612,7 @@
       </c>
       <c r="O84" s="53" t="inlineStr">
         <is>
-          <t>ATT-07 → ligne 990</t>
+          <t>ATT-07 → ligne 1017</t>
         </is>
       </c>
     </row>
@@ -10539,7 +11725,7 @@
       </c>
       <c r="N86" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10 (commit 5b98316, même branche) : e-mail d'attestation avec le numéro EMBF, le lien vers l'attestation et le lien de vérification, envoyé à la première délivrance. À retester en ligne après fusion.</t>
+          <t>Développé le 15/10 (commit 5b98316, fusionné dans main) : e-mail d'attestation avec le numéro EMBF, le lien vers l'attestation et le lien de vérification, envoyé à la première délivrance. À retester en ligne après déploiement.</t>
         </is>
       </c>
       <c r="O86" s="33" t="n"/>
@@ -10821,8 +12007,8 @@
       </c>
       <c r="O91" s="53" t="inlineStr">
         <is>
-          <t>FOR-05 → ligne 1106
-FOR-05-releve → ligne 1134</t>
+          <t>FOR-05 → ligne 1164
+FOR-05-releve → ligne 1192</t>
         </is>
       </c>
     </row>
@@ -11701,19 +12887,19 @@
           <t>Corrigé le 13/10 : prénom et nom saisis séparément à la création, motif de refus affiché. À retester.</t>
         </is>
       </c>
-      <c r="M106" s="56" t="inlineStr">
+      <c r="M106" s="55" t="inlineStr">
         <is>
           <t>À retester</t>
         </is>
       </c>
       <c r="N106" s="33" t="inlineStr">
         <is>
-          <t>Défaut du 15/10 (500 sur /admin/apprenants) corrigé le soir même (27d835b) et vérifié sur la base en ligne : liste, fiche, historique et formulaire Prénom / Nom s'affichent. La création elle-même reste à rejouer par le testeur avec un compte de test.</t>
+          <t>La page /admin/apprenants s'affiche de nouveau sans erreur (vérifié le 15/10 sur la base en ligne). Reste à rejouer la création d'un apprenant (prénom et nom séparés).</t>
         </is>
       </c>
       <c r="O106" s="53" t="inlineStr">
         <is>
-          <t>ADM-12 → ligne 547 · ADM-12-corrige → ligne 1347</t>
+          <t>ADM-12 → ligne 547</t>
         </is>
       </c>
     </row>
@@ -11823,21 +13009,17 @@
           <t>Développé : export CSV de la liste des apprenants, selon les filtres actifs.</t>
         </is>
       </c>
-      <c r="M108" s="56" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="M108" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
         <is>
-          <t>Corrigé avec ADM-12 : l'export CSV produit les 10 comptes affichés (13 colonnes), filtres respectés. Vérifié le 15/10 au soir.</t>
-        </is>
-      </c>
-      <c r="O108" s="53" t="inlineStr">
-        <is>
-          <t>ADM-12-corrige → ligne 1347</t>
-        </is>
-      </c>
+          <t>La page s'affichant de nouveau, l'export CSV est accessible : à rejouer.</t>
+        </is>
+      </c>
+      <c r="O108" s="33" t="n"/>
     </row>
     <row r="109" ht="27" customHeight="1" s="31">
       <c r="A109" s="33" t="inlineStr">
@@ -12217,8 +13399,8 @@
       </c>
       <c r="O114" s="53" t="inlineStr">
         <is>
-          <t>ADM-20 → ligne 575
-ADM-20-editeur → ligne 656</t>
+          <t>ADM-20 → ligne 602
+ADM-20-editeur → ligne 683</t>
         </is>
       </c>
     </row>
@@ -12295,7 +13477,7 @@
       </c>
       <c r="O115" s="53" t="inlineStr">
         <is>
-          <t>ADM-21 → ligne 684</t>
+          <t>ADM-21 → ligne 711</t>
         </is>
       </c>
     </row>
@@ -12372,7 +13554,7 @@
       </c>
       <c r="O116" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 712</t>
+          <t>ADM-22 → ligne 739</t>
         </is>
       </c>
     </row>
@@ -12449,7 +13631,7 @@
       </c>
       <c r="O117" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 712</t>
+          <t>ADM-22 → ligne 739</t>
         </is>
       </c>
     </row>
@@ -12526,7 +13708,7 @@
       </c>
       <c r="O118" s="53" t="inlineStr">
         <is>
-          <t>ADM-22 → ligne 712</t>
+          <t>ADM-22 → ligne 739</t>
         </is>
       </c>
     </row>
@@ -13242,8 +14424,16 @@
           <t>Testé le 15/10 sur la base en ligne avec la clé publique : 43 tables sur 45 refusent (401). visionnages et reglages_attestation répondent 200 mais vide (RLS filtre tout) : le droit de lecture n'a pas été retiré comme ailleurs, à aligner.</t>
         </is>
       </c>
-      <c r="M130" s="33" t="n"/>
-      <c r="N130" s="33" t="n"/>
+      <c r="M130" s="55" t="inlineStr">
+        <is>
+          <t>À retester</t>
+        </is>
+      </c>
+      <c r="N130" s="33" t="inlineStr">
+        <is>
+          <t>Migration 37 écrite : RLS activé et droits retirés sur toutes les tables, y compris visionnages et reglages_attestation. À exécuter sur la base hébergée, puis revérifier avec la clé publique.</t>
+        </is>
+      </c>
       <c r="O130" s="33" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="31">
@@ -13371,7 +14561,7 @@
       </c>
       <c r="N132" s="33" t="inlineStr">
         <is>
-          <t>Le 15/10, 6 comptes sur 7 acceptent encore le mot de passe de démonstration, dont l'administrateur principal cossi@bigfiveabidjan.com (seul jeanluc@ a été changé). Retiré du README le 15/10 ; script npm run auth:renouveler prêt, à lancer par Big Five (voir « En attente client », D2).</t>
+          <t>Le 15/10, le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié dans le README. À changer immédiatement (jeanluc@ a déjà été changé).</t>
         </is>
       </c>
       <c r="O132" s="33" t="n"/>
@@ -14230,14 +15420,14 @@
           <t>npm run typecheck échoue le 15/10 : 5 erreurs TS2321 « Excessive stack depth » sur app/components/admin/Referentiels.vue:64 (typage des routes de $fetch). Sans effet sur le build.</t>
         </is>
       </c>
-      <c r="M146" s="56" t="inlineStr">
-        <is>
-          <t>KO</t>
+      <c r="M146" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N146" s="33" t="inlineStr">
         <is>
-          <t>Inchangé : 5 erreurs TS2321 sur app/components/admin/Referentiels.vue. Sans effet sur le build.</t>
+          <t>npm run typecheck passe sans aucune erreur le 15/10 au soir (Referentiels.vue corrigé).</t>
         </is>
       </c>
       <c r="O146" s="33" t="n"/>
@@ -15347,46 +16537,45 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="O15" location="'Captures'!B1263" display="VIT-11-accueil → ligne 1263&#10;BLQ-CATALOGUE → ligne 4"/>
-    <hyperlink ref="O16" location="'Captures'!B1291" display="VIT-12-fiche → ligne 1291"/>
+    <hyperlink ref="O15" location="'Captures'!B1321" display="VIT-11-accueil → ligne 1321&#10;BLQ-CATALOGUE → ligne 4"/>
+    <hyperlink ref="O16" location="'Captures'!B1349" display="VIT-12-fiche → ligne 1349"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId1"/>
-    <hyperlink ref="O19" location="'Captures'!B1319" display="VIT-15 → ligne 1319"/>
+    <hyperlink ref="O19" location="'Captures'!B1377" display="VIT-15 → ligne 1377"/>
     <hyperlink ref="O24" location="'Captures'!B127" display="BLQ-JURIDIQUE → ligne 127"/>
     <hyperlink ref="O32" location="'Captures'!B272" display="ACH-03 → ligne 272"/>
     <hyperlink ref="O33" location="'Captures'!B306" display="ACH-04 → ligne 306&#10;ACH-04-wave → ligne 414&#10;ACH-04-carte → ligne 340&#10;ACH-04-prefill → ligne 378"/>
-    <hyperlink ref="O34" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66&#10;ADM-20 → ligne 575"/>
+    <hyperlink ref="O34" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66&#10;ADM-20 → ligne 602"/>
     <hyperlink ref="O35" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66"/>
     <hyperlink ref="O36" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66&#10;BLQ-KYC → ligne 155"/>
     <hyperlink ref="O37" location="'Captures'!B66" display="BLQ-FEEXPAY → ligne 66"/>
     <hyperlink ref="O41" location="'Captures'!B452" display="ACH-12 → ligne 452"/>
-    <hyperlink ref="O44" location="'Captures'!B754" display="APP-03 → ligne 754"/>
+    <hyperlink ref="O44" location="'Captures'!B781" display="APP-03 → ligne 781"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId2"/>
-    <hyperlink ref="O46" location="'Captures'!B782" display="APP-05 → ligne 782"/>
+    <hyperlink ref="O46" location="'Captures'!B809" display="APP-05 → ligne 809"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId3"/>
-    <hyperlink ref="O48" location="'Captures'!B810" display="APP-07 → ligne 810&#10;APP-07-mobile → ligne 838"/>
+    <hyperlink ref="O48" location="'Captures'!B837" display="APP-07 → ligne 837&#10;APP-07-mobile → ligne 865"/>
     <hyperlink ref="O59" location="'Captures'!B184" display="BLQ-VIDEOS → ligne 184"/>
-    <hyperlink ref="O62" location="'Captures'!B1018" display="COL-01 → ligne 1018"/>
-    <hyperlink ref="O64" location="'Captures'!B1050" display="COL-03 → ligne 1050"/>
-    <hyperlink ref="O66" location="'Captures'!B1078" display="COL-05-seance-passee → ligne 1078"/>
-    <hyperlink ref="O67" location="'Captures'!B1018" display="COL-01 → ligne 1018"/>
-    <hyperlink ref="O71" location="'Captures'!B1162" display="PRI-02 → ligne 1162&#10;PRI-02-admin → ligne 1190"/>
-    <hyperlink ref="O73" location="'Captures'!B1235" display="PRI-04 → ligne 1235"/>
-    <hyperlink ref="O82" location="'Captures'!B925" display="ATT-05 → ligne 925"/>
-    <hyperlink ref="O83" location="'Captures'!B990" display="ATT-07 → ligne 990"/>
-    <hyperlink ref="O84" location="'Captures'!B990" display="ATT-07 → ligne 990"/>
-    <hyperlink ref="O91" location="'Captures'!B1106" display="FOR-05 → ligne 1106&#10;FOR-05-releve → ligne 1134"/>
+    <hyperlink ref="O62" location="'Captures'!B1045" display="COL-01 → ligne 1045"/>
+    <hyperlink ref="O64" location="'Captures'!B1077" display="COL-03 → ligne 1077"/>
+    <hyperlink ref="O66" location="'Captures'!B1136" display="COL-05-seance-passee → ligne 1136"/>
+    <hyperlink ref="O67" location="'Captures'!B1045" display="COL-01 → ligne 1045"/>
+    <hyperlink ref="O71" location="'Captures'!B1220" display="PRI-02 → ligne 1220&#10;PRI-02-admin → ligne 1248"/>
+    <hyperlink ref="O73" location="'Captures'!B1293" display="PRI-04 → ligne 1293"/>
+    <hyperlink ref="O82" location="'Captures'!B952" display="ATT-05 → ligne 952"/>
+    <hyperlink ref="O83" location="'Captures'!B1017" display="ATT-07 → ligne 1017"/>
+    <hyperlink ref="O84" location="'Captures'!B1017" display="ATT-07 → ligne 1017"/>
+    <hyperlink ref="O91" location="'Captures'!B1164" display="FOR-05 → ligne 1164&#10;FOR-05-releve → ligne 1192"/>
     <hyperlink ref="O99" location="'Captures'!B491" display="ADM-05 → ligne 491"/>
     <hyperlink ref="O100" location="'Captures'!B519" display="ADM-06 → ligne 519"/>
     <hyperlink ref="O101" location="'Captures'!B519" display="ADM-06 → ligne 519"/>
     <hyperlink ref="O106" location="'Captures'!B547" display="ADM-12 → ligne 547"/>
-    <hyperlink ref="O108" location="'Captures'!B547" display="ADM-12 → ligne 547"/>
     <hyperlink ref="O111" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
     <hyperlink ref="O112" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
-    <hyperlink ref="O114" location="'Captures'!B575" display="ADM-20 → ligne 575&#10;ADM-20-editeur → ligne 656"/>
-    <hyperlink ref="O115" location="'Captures'!B684" display="ADM-21 → ligne 684"/>
-    <hyperlink ref="O116" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
-    <hyperlink ref="O117" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
-    <hyperlink ref="O118" location="'Captures'!B712" display="ADM-22 → ligne 712"/>
+    <hyperlink ref="O114" location="'Captures'!B602" display="ADM-20 → ligne 602&#10;ADM-20-editeur → ligne 683"/>
+    <hyperlink ref="O115" location="'Captures'!B711" display="ADM-21 → ligne 711"/>
+    <hyperlink ref="O116" location="'Captures'!B739" display="ADM-22 → ligne 739"/>
+    <hyperlink ref="O117" location="'Captures'!B739" display="ADM-22 → ligne 739"/>
+    <hyperlink ref="O118" location="'Captures'!B739" display="ADM-22 → ligne 739"/>
     <hyperlink ref="O120" location="'Captures'!B452" display="ACH-12 → ligne 452"/>
     <hyperlink ref="O142" location="'Captures'!B37" display="BLQ-CONFIG → ligne 37"/>
     <hyperlink ref="O143" location="'Captures'!B95" display="BLQ-GA4 → ligne 95"/>
@@ -15430,6 +16619,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -17932,6 +19122,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -19792,6 +20983,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -20821,6 +22013,7 @@
       </c>
       <c r="G32" s="33" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="45" customHeight="1" s="31">
       <c r="A34" s="43" t="inlineStr">
         <is>
@@ -20828,6 +22021,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="58" t="inlineStr">
         <is>
@@ -21077,6 +22271,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -22392,6 +23587,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -24032,6 +25228,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -24267,6 +25464,7 @@
       </c>
       <c r="E12" s="33" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="31.5" customHeight="1" s="31">
       <c r="A14" s="4" t="inlineStr">
         <is>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -531,6 +531,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -556,6 +559,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -581,6 +587,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -606,6 +615,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -631,6 +643,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -656,6 +671,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -681,6 +699,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -706,6 +727,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -731,6 +755,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -756,6 +783,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -781,6 +811,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -806,6 +839,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -831,6 +867,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -856,6 +895,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -881,6 +923,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -906,6 +951,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -931,6 +979,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -956,6 +1007,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -981,6 +1035,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1006,6 +1063,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1031,6 +1091,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1056,6 +1119,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1081,6 +1147,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1106,6 +1175,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1131,6 +1203,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1156,6 +1231,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1181,6 +1259,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1206,6 +1287,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1231,6 +1315,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1256,6 +1343,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1281,6 +1371,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1306,6 +1399,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1331,6 +1427,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1356,6 +1455,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1381,6 +1483,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1406,6 +1511,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1431,6 +1539,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1456,6 +1567,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1481,6 +1595,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1506,6 +1623,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1804,7 +1924,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -2209,7 +2328,7 @@
     <row r="44" ht="27.75" customHeight="1" s="31">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>• Mot de passe de démonstration commun encore actif sur tous les comptes et écrit dans le README.</t>
+          <t>• Mot de passe de démonstration commun encore actif sur 6 comptes sur 7 ; retiré du README le 15/10, script de renouvellement prêt (D2).</t>
         </is>
       </c>
     </row>
@@ -2230,14 +2349,14 @@
     <row r="47" ht="27.75" customHeight="1" s="31">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>• /admin/apprenants plante (erreur 500) depuis le 15/10 : création et export d'apprenants indisponibles — reste dev (D1).</t>
+          <t>• /admin/apprenants : l'erreur 500 du 15/10 est corrigée (27d835b) et vérifiée ; reste à rejouer la création d'un apprenant (ADM-12).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="27.75" customHeight="1" s="31">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié — à changer immédiatement (D2).</t>
+          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration : lancer npm run auth:renouveler -- --appliquer (D2).</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1378"/>
+  <dimension ref="B1:B1378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -4110,7 +4229,7 @@
     <row r="575">
       <c r="B575" s="59" t="inlineStr">
         <is>
-          <t>ADM-12-corrige — capture complémentaire</t>
+          <t>ADM-12-corrige — /admin/apprenants s'affiche de nouveau (corrigé le 15/10, 27d835b)</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4909,7 @@
     <row r="1105">
       <c r="B1105" s="59" t="inlineStr">
         <is>
-          <t>COL-05-corrige — capture complémentaire</t>
+          <t>COL-05-corrige — Séance du 19/09 affichée « TERMINÉE · 19 septembre à 20:00 » (corrigé le 15/10)</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5334,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -5857,8 +5975,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
         <is>
@@ -5921,7 +6037,7 @@
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>Corrigé</t>
+          <t>Corrigé (27d835b)</t>
         </is>
       </c>
       <c r="D24" s="50" t="inlineStr">
@@ -5931,7 +6047,7 @@
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>La page s'affiche de nouveau sans erreur (vérifié le 15/10 sur la base en ligne).</t>
+          <t>La page s'affiche de nouveau sans erreur (vérifié le 15/10 sur la base en ligne). Cause : une fusion a gardé l'API qui renvoie { apprenants, choix } et repris un écran qui attend une simple liste ; l'écran lit désormais la liste.</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
@@ -5941,12 +6057,13 @@
       </c>
       <c r="G24" s="50" t="inlineStr">
         <is>
-          <t>Rejouer la création et l’export.</t>
+          <t>Vérifié le 15/10 : liste des 10 comptes, fiche, historique, export CSV (10 lignes, 13 colonnes), formulaire Prénom / Nom. Reste au testeur : créer un apprenant de test (ADM-12), non rejoué pour ne rien écrire en base.</t>
         </is>
       </c>
       <c r="H24" s="51" t="inlineStr">
         <is>
-          <t>ADM-12 → Captures, ligne 547</t>
+          <t>ADM-12 → Captures, ligne 547
+ADM-12-corrige → Captures, ligne 575</t>
         </is>
       </c>
     </row>
@@ -5958,12 +6075,12 @@
       </c>
       <c r="B25" s="49" t="inlineStr">
         <is>
-          <t>Mot de passe de démonstration encore actif sur un administrateur principal</t>
+          <t>Mots de passe de démonstration encore actifs (dont l'administrateur principal)</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>Développement + Big Five</t>
+          <t>Big Five (lancer le script)</t>
         </is>
       </c>
       <c r="D25" s="50" t="inlineStr">
@@ -5973,7 +6090,7 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>cossi@bigfiveabidjan.com s'ouvre avec le mot de passe publié dans le README.</t>
+          <t>Lecture du 15/10 sur la base en ligne : 6 comptes sur 7 acceptent encore le mot de passe commun du jeu de données — cossi@, jeremie.declercq@, houefa@bigfiveabidjan.com, editeur@bigfive.ci, formateur@bigfive.ci, aya@example.ci. Seul jeanluc@ l'a changé.</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -5983,7 +6100,7 @@
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>Retiré du README le 15/10. Reste à changer le mot de passe de cossi@ et des autres comptes du jeu de données.</t>
+          <t>Mot de passe retiré du README et du TODO le 15/10. Script prêt : npm run auth:renouveler (lecture seule) puis npm run auth:renouveler -- --appliquer, qui tire un mot de passe aléatoire par compte et l'affiche une seule fois dans le terminal : le reporter dans un gestionnaire, le transmettre à son titulaire. Puis remplacer NUXT_SESSION_PASSWORD sur Vercel pour fermer les sessions ouvertes.</t>
         </is>
       </c>
       <c r="H25" s="50" t="inlineStr">
@@ -6005,7 +6122,7 @@
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>Corrigé (dans main)</t>
+          <t>Corrigé (27d835b)</t>
         </is>
       </c>
       <c r="D26" s="50" t="inlineStr">
@@ -6025,12 +6142,13 @@
       </c>
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>Corrigé : une séance passée affiche « Terminée ».</t>
+          <t>Vérifié le 15/10 : la séance du 19/09 affiche « TERMINÉE · 19 septembre à 20:00 » et « Cette séance s'est terminée », bouton d'entrée grisé, y compris pour le formateur et l'administrateur.</t>
         </is>
       </c>
       <c r="H26" s="51" t="inlineStr">
         <is>
-          <t>COL-05-seance-passee → Captures, ligne 1136</t>
+          <t>COL-05-seance-passee → Captures, ligne 1136
+COL-05-corrige → Captures, ligne 1105</t>
         </is>
       </c>
     </row>
@@ -6286,8 +6404,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
         <is>
@@ -6695,7 +6811,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -10512,12 +10627,12 @@
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>Zoom en réel depuis le 15/10. Création automatique validée : la session ses-010 créée depuis le site à 19:53 a reçu la réunion 83441083225, présente chez Zoom sous le compte cossi@bigfiveabidjan.com (2 h, salle d'attente). Restent à dérouler : entrée formateur et apprenant depuis la plateforme, report et annulation d'une réunion réelle. Une séance passée s'affichait « EN DIRECT » : corrigé.</t>
+          <t>Zoom en réel depuis le 15/10. Création automatique validée : la session ses-010 créée depuis le site à 19:53 a reçu la réunion 83441083225, présente chez Zoom sous le compte cossi@bigfiveabidjan.com (2 h, salle d'attente). Restent à dérouler : entrée formateur et apprenant depuis la plateforme, report et annulation d'une réunion réelle. Une séance passée s'affichait « EN DIRECT · 621 h » : corrigé (27d835b) et vérifié le 15/10, elle affiche « TERMINÉE · 19 septembre à 20:00 ».</t>
         </is>
       </c>
       <c r="O66" s="53" t="inlineStr">
         <is>
-          <t>COL-05-seance-passee → ligne 1136</t>
+          <t>COL-05-seance-passee → ligne 1136 · COL-05-corrige → ligne 1105</t>
         </is>
       </c>
     </row>
@@ -12899,7 +13014,7 @@
       </c>
       <c r="O106" s="53" t="inlineStr">
         <is>
-          <t>ADM-12 → ligne 547</t>
+          <t>ADM-12 → ligne 547 · ADM-12-corrige → ligne 575</t>
         </is>
       </c>
     </row>
@@ -13011,15 +13126,19 @@
       </c>
       <c r="M108" s="55" t="inlineStr">
         <is>
-          <t>À retester</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
         <is>
-          <t>La page s'affichant de nouveau, l'export CSV est accessible : à rejouer.</t>
-        </is>
-      </c>
-      <c r="O108" s="33" t="n"/>
+          <t>Corrigé avec ADM-12 : l'export CSV produit les 10 comptes affichés (13 colonnes), filtres respectés. Vérifié le 15/10 au soir.</t>
+        </is>
+      </c>
+      <c r="O108" s="33" t="inlineStr">
+        <is>
+          <t>ADM-12-corrige → ligne 575</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="27" customHeight="1" s="31">
       <c r="A109" s="33" t="inlineStr">
@@ -14561,7 +14680,7 @@
       </c>
       <c r="N132" s="33" t="inlineStr">
         <is>
-          <t>Le 15/10, le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration publié dans le README. À changer immédiatement (jeanluc@ a déjà été changé).</t>
+          <t>Le 15/10, 6 comptes sur 7 acceptent encore le mot de passe de démonstration, dont l'administrateur principal cossi@bigfiveabidjan.com (seul jeanluc@ a été changé). Retiré du README le 15/10 ; script npm run auth:renouveler prêt, à lancer par Big Five (voir « En attente client », D2).</t>
         </is>
       </c>
       <c r="O132" s="33" t="n"/>
@@ -16619,7 +16738,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -19122,7 +19240,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -20983,7 +21100,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -22013,7 +22129,6 @@
       </c>
       <c r="G32" s="33" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="45" customHeight="1" s="31">
       <c r="A34" s="43" t="inlineStr">
         <is>
@@ -22021,7 +22136,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="58" t="inlineStr">
         <is>
@@ -22271,7 +22385,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -23587,7 +23700,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -25228,7 +25340,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="31">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -25464,7 +25575,6 @@
       </c>
       <c r="E12" s="33" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14" ht="31.5" customHeight="1" s="31">
       <c r="A14" s="4" t="inlineStr">
         <is>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -2293,28 +2293,28 @@
     <row r="39" ht="27.75" customHeight="1" s="31">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>• FeexPay — Orange, MTN et Moov ouverts en live, webhook opérationnel (paiement MTN réel du 15/10 refusé par MTN pour solde ou plafond, et tracé). Wave : Clé agrégée Wave à activer (C14). Carte : KYC carte en brouillon (C1) — actions Big Five.</t>
+          <t>• FeexPay — Mobile Money validé en réel le 15/10 : Orange et MTN à 200 F réussis, modules ouverts, webhook opérationnel. Wave : Clé agrégée Wave à activer (C14). Carte : KYC carte en brouillon (C1) — actions Big Five.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="27.75" customHeight="1" s="31">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>• Envoi d'e-mails — aucun pilote réel : mot de passe oublié, confirmation d'achat, attestation et avis d'annulation ne partent pas.</t>
+          <t>• E-mails — Resend en service depuis le 15/10 (réinitialisation délivrée, avis d'annulation envoyé). Confirmation d'achat et attestation : écrites et fusionnées, à vérifier après déploiement. Un seul DMARC à garder (C3).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="27.75" customHeight="1" s="31">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>• Vidéos — 15 chapitres rattachés sur 72 dans la base en ligne.</t>
+          <t>• Vidéos — 15 chapitres rattachés sur 72 dans la base en ligne ; lecture vérifiée sur le domaine définitif (Worker vidéo autorisé le 15/10).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1" s="31">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>• Zoom — réglé le 15/10 (app activée, clés posées, mode live) ; reste le test réel de bout en bout (Z6 à Z9).</t>
+          <t>• Zoom — en réel depuis le 15/10 : la session ses-010 a créé sa réunion chez Zoom ; reste l'entrée en salle, le report et l'annulation (Z7 à Z9).</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="59" t="inlineStr">
         <is>
@@ -3471,37 +3470,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="59" t="inlineStr">
         <is>
@@ -3516,33 +3484,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
     <row r="66">
       <c r="B66" s="59" t="inlineStr">
         <is>
@@ -3557,33 +3498,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
     <row r="95">
       <c r="B95" s="59" t="inlineStr">
         <is>
@@ -3598,36 +3512,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
     <row r="127">
       <c r="B127" s="59" t="inlineStr">
         <is>
@@ -3642,32 +3526,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
     <row r="155">
       <c r="B155" s="59" t="inlineStr">
         <is>
@@ -3682,33 +3540,6 @@
         </is>
       </c>
     </row>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
     <row r="184">
       <c r="B184" s="59" t="inlineStr">
         <is>
@@ -3723,63 +3554,6 @@
         </is>
       </c>
     </row>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
     <row r="243">
       <c r="B243" s="59" t="inlineStr">
         <is>
@@ -3787,34 +3561,6 @@
         </is>
       </c>
     </row>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
     <row r="272">
       <c r="B272" s="59" t="inlineStr">
         <is>
@@ -3829,38 +3575,6 @@
         </is>
       </c>
     </row>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
     <row r="306">
       <c r="B306" s="59" t="inlineStr">
         <is>
@@ -3875,38 +3589,6 @@
         </is>
       </c>
     </row>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
     <row r="340">
       <c r="B340" s="59" t="inlineStr">
         <is>
@@ -3921,42 +3603,6 @@
         </is>
       </c>
     </row>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
     <row r="378">
       <c r="B378" s="59" t="inlineStr">
         <is>
@@ -3971,40 +3617,6 @@
         </is>
       </c>
     </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
     <row r="414">
       <c r="B414" s="59" t="inlineStr">
         <is>
@@ -4019,42 +3631,6 @@
         </is>
       </c>
     </row>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
     <row r="452">
       <c r="B452" s="59" t="inlineStr">
         <is>
@@ -4069,43 +3645,6 @@
         </is>
       </c>
     </row>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
     <row r="491">
       <c r="B491" s="59" t="inlineStr">
         <is>
@@ -4120,32 +3659,6 @@
         </is>
       </c>
     </row>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
     <row r="519">
       <c r="B519" s="59" t="inlineStr">
         <is>
@@ -4160,32 +3673,6 @@
         </is>
       </c>
     </row>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
     <row r="547">
       <c r="B547" s="59" t="inlineStr">
         <is>
@@ -4200,32 +3687,6 @@
         </is>
       </c>
     </row>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
     <row r="575">
       <c r="B575" s="59" t="inlineStr">
         <is>
@@ -4233,32 +3694,6 @@
         </is>
       </c>
     </row>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
     <row r="602">
       <c r="B602" s="59" t="inlineStr">
         <is>
@@ -4273,85 +3708,6 @@
         </is>
       </c>
     </row>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
     <row r="683">
       <c r="B683" s="59" t="inlineStr">
         <is>
@@ -4366,32 +3722,6 @@
         </is>
       </c>
     </row>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
     <row r="711">
       <c r="B711" s="59" t="inlineStr">
         <is>
@@ -4406,32 +3736,6 @@
         </is>
       </c>
     </row>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
     <row r="739">
       <c r="B739" s="59" t="inlineStr">
         <is>
@@ -4446,46 +3750,6 @@
         </is>
       </c>
     </row>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
     <row r="781">
       <c r="B781" s="59" t="inlineStr">
         <is>
@@ -4500,32 +3764,6 @@
         </is>
       </c>
     </row>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
     <row r="809">
       <c r="B809" s="59" t="inlineStr">
         <is>
@@ -4540,32 +3778,6 @@
         </is>
       </c>
     </row>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
     <row r="837">
       <c r="B837" s="59" t="inlineStr">
         <is>
@@ -4580,32 +3792,6 @@
         </is>
       </c>
     </row>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
     <row r="865">
       <c r="B865" s="59" t="inlineStr">
         <is>
@@ -4620,91 +3806,6 @@
         </is>
       </c>
     </row>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
     <row r="952">
       <c r="B952" s="59" t="inlineStr">
         <is>
@@ -4719,69 +3820,6 @@
         </is>
       </c>
     </row>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
     <row r="1017">
       <c r="B1017" s="59" t="inlineStr">
         <is>
@@ -4796,32 +3834,6 @@
         </is>
       </c>
     </row>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
     <row r="1045">
       <c r="B1045" s="59" t="inlineStr">
         <is>
@@ -4836,36 +3848,6 @@
         </is>
       </c>
     </row>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
     <row r="1077">
       <c r="B1077" s="59" t="inlineStr">
         <is>
@@ -4880,32 +3862,6 @@
         </is>
       </c>
     </row>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
     <row r="1105">
       <c r="B1105" s="59" t="inlineStr">
         <is>
@@ -4913,36 +3869,6 @@
         </is>
       </c>
     </row>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
     <row r="1136">
       <c r="B1136" s="59" t="inlineStr">
         <is>
@@ -4957,32 +3883,6 @@
         </is>
       </c>
     </row>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
     <row r="1164">
       <c r="B1164" s="59" t="inlineStr">
         <is>
@@ -4997,32 +3897,6 @@
         </is>
       </c>
     </row>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178"/>
-    <row r="1179"/>
-    <row r="1180"/>
-    <row r="1181"/>
-    <row r="1182"/>
-    <row r="1183"/>
-    <row r="1184"/>
-    <row r="1185"/>
-    <row r="1186"/>
-    <row r="1187"/>
-    <row r="1188"/>
-    <row r="1189"/>
-    <row r="1190"/>
-    <row r="1191"/>
     <row r="1192">
       <c r="B1192" s="59" t="inlineStr">
         <is>
@@ -5037,32 +3911,6 @@
         </is>
       </c>
     </row>
-    <row r="1194"/>
-    <row r="1195"/>
-    <row r="1196"/>
-    <row r="1197"/>
-    <row r="1198"/>
-    <row r="1199"/>
-    <row r="1200"/>
-    <row r="1201"/>
-    <row r="1202"/>
-    <row r="1203"/>
-    <row r="1204"/>
-    <row r="1205"/>
-    <row r="1206"/>
-    <row r="1207"/>
-    <row r="1208"/>
-    <row r="1209"/>
-    <row r="1210"/>
-    <row r="1211"/>
-    <row r="1212"/>
-    <row r="1213"/>
-    <row r="1214"/>
-    <row r="1215"/>
-    <row r="1216"/>
-    <row r="1217"/>
-    <row r="1218"/>
-    <row r="1219"/>
     <row r="1220">
       <c r="B1220" s="59" t="inlineStr">
         <is>
@@ -5077,32 +3925,6 @@
         </is>
       </c>
     </row>
-    <row r="1222"/>
-    <row r="1223"/>
-    <row r="1224"/>
-    <row r="1225"/>
-    <row r="1226"/>
-    <row r="1227"/>
-    <row r="1228"/>
-    <row r="1229"/>
-    <row r="1230"/>
-    <row r="1231"/>
-    <row r="1232"/>
-    <row r="1233"/>
-    <row r="1234"/>
-    <row r="1235"/>
-    <row r="1236"/>
-    <row r="1237"/>
-    <row r="1238"/>
-    <row r="1239"/>
-    <row r="1240"/>
-    <row r="1241"/>
-    <row r="1242"/>
-    <row r="1243"/>
-    <row r="1244"/>
-    <row r="1245"/>
-    <row r="1246"/>
-    <row r="1247"/>
     <row r="1248">
       <c r="B1248" s="59" t="inlineStr">
         <is>
@@ -5117,49 +3939,6 @@
         </is>
       </c>
     </row>
-    <row r="1250"/>
-    <row r="1251"/>
-    <row r="1252"/>
-    <row r="1253"/>
-    <row r="1254"/>
-    <row r="1255"/>
-    <row r="1256"/>
-    <row r="1257"/>
-    <row r="1258"/>
-    <row r="1259"/>
-    <row r="1260"/>
-    <row r="1261"/>
-    <row r="1262"/>
-    <row r="1263"/>
-    <row r="1264"/>
-    <row r="1265"/>
-    <row r="1266"/>
-    <row r="1267"/>
-    <row r="1268"/>
-    <row r="1269"/>
-    <row r="1270"/>
-    <row r="1271"/>
-    <row r="1272"/>
-    <row r="1273"/>
-    <row r="1274"/>
-    <row r="1275"/>
-    <row r="1276"/>
-    <row r="1277"/>
-    <row r="1278"/>
-    <row r="1279"/>
-    <row r="1280"/>
-    <row r="1281"/>
-    <row r="1282"/>
-    <row r="1283"/>
-    <row r="1284"/>
-    <row r="1285"/>
-    <row r="1286"/>
-    <row r="1287"/>
-    <row r="1288"/>
-    <row r="1289"/>
-    <row r="1290"/>
-    <row r="1291"/>
-    <row r="1292"/>
     <row r="1293">
       <c r="B1293" s="59" t="inlineStr">
         <is>
@@ -5174,32 +3953,6 @@
         </is>
       </c>
     </row>
-    <row r="1295"/>
-    <row r="1296"/>
-    <row r="1297"/>
-    <row r="1298"/>
-    <row r="1299"/>
-    <row r="1300"/>
-    <row r="1301"/>
-    <row r="1302"/>
-    <row r="1303"/>
-    <row r="1304"/>
-    <row r="1305"/>
-    <row r="1306"/>
-    <row r="1307"/>
-    <row r="1308"/>
-    <row r="1309"/>
-    <row r="1310"/>
-    <row r="1311"/>
-    <row r="1312"/>
-    <row r="1313"/>
-    <row r="1314"/>
-    <row r="1315"/>
-    <row r="1316"/>
-    <row r="1317"/>
-    <row r="1318"/>
-    <row r="1319"/>
-    <row r="1320"/>
     <row r="1321">
       <c r="B1321" s="59" t="inlineStr">
         <is>
@@ -5214,32 +3967,6 @@
         </is>
       </c>
     </row>
-    <row r="1323"/>
-    <row r="1324"/>
-    <row r="1325"/>
-    <row r="1326"/>
-    <row r="1327"/>
-    <row r="1328"/>
-    <row r="1329"/>
-    <row r="1330"/>
-    <row r="1331"/>
-    <row r="1332"/>
-    <row r="1333"/>
-    <row r="1334"/>
-    <row r="1335"/>
-    <row r="1336"/>
-    <row r="1337"/>
-    <row r="1338"/>
-    <row r="1339"/>
-    <row r="1340"/>
-    <row r="1341"/>
-    <row r="1342"/>
-    <row r="1343"/>
-    <row r="1344"/>
-    <row r="1345"/>
-    <row r="1346"/>
-    <row r="1347"/>
-    <row r="1348"/>
     <row r="1349">
       <c r="B1349" s="59" t="inlineStr">
         <is>
@@ -5254,32 +3981,6 @@
         </is>
       </c>
     </row>
-    <row r="1351"/>
-    <row r="1352"/>
-    <row r="1353"/>
-    <row r="1354"/>
-    <row r="1355"/>
-    <row r="1356"/>
-    <row r="1357"/>
-    <row r="1358"/>
-    <row r="1359"/>
-    <row r="1360"/>
-    <row r="1361"/>
-    <row r="1362"/>
-    <row r="1363"/>
-    <row r="1364"/>
-    <row r="1365"/>
-    <row r="1366"/>
-    <row r="1367"/>
-    <row r="1368"/>
-    <row r="1369"/>
-    <row r="1370"/>
-    <row r="1371"/>
-    <row r="1372"/>
-    <row r="1373"/>
-    <row r="1374"/>
-    <row r="1375"/>
-    <row r="1376"/>
     <row r="1377">
       <c r="B1377" s="59" t="inlineStr">
         <is>
@@ -16816,7 +15517,7 @@
       </c>
       <c r="H5" s="33" t="inlineStr">
         <is>
-          <t>Intégration faite — voir « Passage en production »</t>
+          <t>Live en service le 15/10 pour le Mobile Money ; Wave et carte à activer chez FeexPay</t>
         </is>
       </c>
     </row>
@@ -16841,7 +15542,7 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F6" s="33" t="inlineStr">
@@ -16854,7 +15555,11 @@
           <t>3 à 5 jours</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n"/>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 (Resend) — garder un seul DMARC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="39" t="n">
@@ -17033,7 +15738,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F11" s="33" t="inlineStr">
@@ -17048,7 +15753,7 @@
       </c>
       <c r="H11" s="33" t="inlineStr">
         <is>
-          <t>Voir « Passage en production »</t>
+          <t>Fait le 15/10 (réunions créées automatiquement)</t>
         </is>
       </c>
     </row>
@@ -17382,7 +16087,11 @@
           <t>immédiat</t>
         </is>
       </c>
-      <c r="H20" s="33" t="n"/>
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>Script prêt : npm run auth:renouveler -- --appliquer (à lancer par Big Five)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="31">
       <c r="A21" s="39" t="n">
@@ -17477,7 +16186,7 @@
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F23" s="33" t="inlineStr">
@@ -17490,7 +16199,11 @@
           <t>2 jours</t>
         </is>
       </c>
-      <c r="H23" s="33" t="n"/>
+      <c r="H23" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 (pilote Resend)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="31">
       <c r="A24" s="39" t="n">
@@ -17528,7 +16241,7 @@
       </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Opérationnel (clé Bearer), vérifié en réel le 15/10</t>
         </is>
       </c>
     </row>
@@ -17566,7 +16279,11 @@
           <t>3 jours</t>
         </is>
       </c>
-      <c r="H25" s="33" t="n"/>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>Développé le 15/10 : relance quotidienne des commandes en attente (2bc3bcc)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="31">
       <c r="A26" s="39" t="n">
@@ -17604,7 +16321,7 @@
       </c>
       <c r="H26" s="33" t="inlineStr">
         <is>
-          <t>Fait — reste la configuration</t>
+          <t>Fait — réunions réelles depuis le 15/10</t>
         </is>
       </c>
     </row>
@@ -17749,7 +16466,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F30" s="33" t="inlineStr">
@@ -17762,7 +16479,11 @@
           <t>1 jour</t>
         </is>
       </c>
-      <c r="H30" s="33" t="n"/>
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>Fait le 15/10 : https://emasterclass.bigfive.solutions/</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="31">
       <c r="A31" s="39" t="n">
@@ -17912,7 +16633,7 @@
       </c>
       <c r="H34" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Corrigé le 15/10 : npm run typecheck sans erreur</t>
         </is>
       </c>
     </row>
@@ -17952,7 +16673,7 @@
       </c>
       <c r="H35" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Migration 37 écrite, à exécuter sur la base hébergée</t>
         </is>
       </c>
     </row>
@@ -17992,7 +16713,7 @@
       </c>
       <c r="H36" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Développé le 15/10, migration 38 à exécuter avant déploiement</t>
         </is>
       </c>
     </row>
@@ -18057,7 +16778,7 @@
       </c>
       <c r="E38" s="40" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F38" s="33" t="inlineStr">
@@ -18072,7 +16793,7 @@
       </c>
       <c r="H38" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10) — preuve BLQ-ZOOM</t>
+          <t>Fait le 15/10</t>
         </is>
       </c>
     </row>
@@ -18112,7 +16833,7 @@
       </c>
       <c r="H39" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Corrigé et vérifié le 15/10 (27d835b)</t>
         </is>
       </c>
     </row>
@@ -18192,7 +16913,7 @@
       </c>
       <c r="H41" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Corrigé et vérifié le 15/10</t>
         </is>
       </c>
     </row>
@@ -18232,7 +16953,7 @@
       </c>
       <c r="H42" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Mobile Money : rattachement par callback_info confirmé sur les paiements réels ; à vérifier sur un paiement carte</t>
         </is>
       </c>
     </row>
@@ -19313,7 +18034,7 @@
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>À fournir</t>
+          <t>En service (boutique « Big Five Abidjan »)</t>
         </is>
       </c>
       <c r="H5" s="33" t="n"/>
@@ -19385,7 +18106,7 @@
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>Fourni (test)</t>
+          <t>Fourni</t>
         </is>
       </c>
       <c r="H7" s="33" t="n"/>
@@ -19457,7 +18178,7 @@
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>À fournir</t>
+          <t>Fourni — en service (15/10)</t>
         </is>
       </c>
       <c r="H9" s="33" t="n"/>
@@ -19493,7 +18214,7 @@
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Fourni (local) — à régénérer pour la production</t>
+          <t>Fait — clé de production posée le 15/10</t>
         </is>
       </c>
       <c r="H10" s="33" t="n"/>
@@ -19529,7 +18250,7 @@
       </c>
       <c r="G11" s="40" t="inlineStr">
         <is>
-          <t>À déclarer après la mise en ligne</t>
+          <t>Déclarée le 15/10 (en-tête Bearer)</t>
         </is>
       </c>
       <c r="H11" s="33" t="n"/>
@@ -19601,7 +18322,7 @@
       </c>
       <c r="G13" s="40" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>Sans objet : la liste d’IP ne sert qu’aux reversements (Payout API)</t>
         </is>
       </c>
       <c r="H13" s="33" t="n"/>
@@ -19637,7 +18358,7 @@
       </c>
       <c r="G14" s="40" t="inlineStr">
         <is>
-          <t>Mobile Money et Wave ouverts ; carte refusée (KYC carte en brouillon, 15/10) : Visa et Djamo masqués</t>
+          <t>Orange, MTN et Moov ouverts ; Wave : Clé agrégée Wave à activer ; carte : KYC carte en brouillon</t>
         </is>
       </c>
       <c r="H14" s="33" t="n"/>
@@ -22435,7 +21156,7 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>Migrations 01 à 05 appliquées et vérifiées le 02/09</t>
+          <t>Migrations 01 à 36 en place ; 37 (droits des clés publiques) et 38 (coaching privé dans Transactions) à exécuter dans SQL Editor avant le déploiement du 15/10 au soir</t>
         </is>
       </c>
     </row>
@@ -22462,7 +21183,7 @@
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>Vérifié le 02/09 : les démonstrations se lisent depuis le CDN, le cloisonnement des chapitres tient</t>
+          <t>Lecture vérifiée le 15/10 sur emasterclass.bigfive.solutions (origine ajoutée au Worker, redéployé)</t>
         </is>
       </c>
     </row>
@@ -22484,12 +21205,12 @@
       </c>
       <c r="D7" s="45" t="inlineStr">
         <is>
-          <t>À fournir — bloquant</t>
+          <t>Fourni — en service</t>
         </is>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>Débloque réinitialisation, confirmation d'achat, envoi d'attestation, avis d'annulation. Aucun pilote d'envoi n'est encore codé : NOTIFICATIONS_DRIVER n'accepte que « console ».</t>
+          <t>Resend, domaine bigfive.solutions vérifié (DKIM, SPF), NOTIFICATIONS_DRIVER=resend depuis le 15/10. Deux enregistrements DMARC coexistent : n'en garder qu'un.</t>
         </is>
       </c>
     </row>
@@ -22538,12 +21259,12 @@
       </c>
       <c r="D9" s="45" t="inlineStr">
         <is>
-          <t>Sandbox en service — live à fournir</t>
+          <t>Live en service — Mobile Money</t>
         </is>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
-          <t>Intégration faite ; les clés live et le compte marchand manquent</t>
+          <t>Orange, MTN et Moov encaissent en réel (paiements de 200 F réussis le 15/10). Wave : Clé agrégée Wave à activer. Carte : KYC carte à faire valider.</t>
         </is>
       </c>
     </row>
@@ -22565,12 +21286,12 @@
       </c>
       <c r="D10" s="45" t="inlineStr">
         <is>
-          <t>À fournir — bloquant</t>
+          <t>Fourni — en service</t>
         </is>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>Intégration faite, mode simulation ; les réunions se créent seules une fois les clés posées</t>
+          <t>ZOOM_MODE=live depuis le 15/10 : app Server-to-Server activée, Meeting SDK configuré, réunions créées automatiquement (ses-010).</t>
         </is>
       </c>
     </row>
@@ -22646,12 +21367,12 @@
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
-          <t>À fournir — bloquant</t>
+          <t>Fourni — en service</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>NUXT_PUBLIC_SITE_URL alimente les canonical, le sitemap et le lien de vérification des attestations ; il pointe encore vers l'URL Vercel</t>
+          <t>URL définitive https://emasterclass.bigfive.solutions/ : CNAME Cloudflare vers Vercel, HTTPS, NUXT_PUBLIC_SITE_URL posé (15/10).</t>
         </is>
       </c>
     </row>
@@ -25390,7 +24111,7 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>Parcours 01 et 02 : FeexPay et Zoom développés, en attente des clés de production</t>
+          <t>Parcours 01 : paiement Mobile Money validé en réel le 15/10. Parcours 02 : réunions Zoom créées automatiquement ; l'entrée en salle reste à tester.</t>
         </is>
       </c>
     </row>
@@ -25471,7 +24192,7 @@
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>La signature se dépose depuis l'administration (21/09) ; l'envoi par e-mail attend un pilote d'envoi réel</t>
+          <t>La signature se dépose depuis l'administration (21/09) ; l'e-mail d'attestation est écrit et fusionné le 15/10, à vérifier après déploiement.</t>
         </is>
       </c>
     </row>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -2328,7 +2328,7 @@
     <row r="44" ht="27.75" customHeight="1" s="31">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>• Mot de passe de démonstration commun encore actif sur 6 comptes sur 7 ; retiré du README le 15/10, script de renouvellement prêt (D2).</t>
+          <t>• Mots de passe de démonstration : renouvelés le 15/10 sur les 6 comptes concernés ; reste à remplacer NUXT_SESSION_PASSWORD sur Vercel et redéployer.</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
     <row r="48" ht="27.75" customHeight="1" s="31">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>• Le compte administrateur principal cossi@bigfiveabidjan.com s'ouvre encore avec le mot de passe de démonstration : lancer npm run auth:renouveler -- --appliquer (D2).</t>
+          <t>• Après le push : exécuter les migrations 37 et 38 (déjà prévu), puis vérifier en ligne les 9 cas « À retester ».</t>
         </is>
       </c>
     </row>
@@ -4035,6 +4035,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -4676,6 +4677,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
         <is>
@@ -4776,12 +4779,12 @@
       </c>
       <c r="B25" s="49" t="inlineStr">
         <is>
-          <t>Mots de passe de démonstration encore actifs (dont l'administrateur principal)</t>
+          <t>Mots de passe de démonstration</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>Big Five (lancer le script)</t>
+          <t>Fait le 15/10</t>
         </is>
       </c>
       <c r="D25" s="50" t="inlineStr">
@@ -4791,7 +4794,7 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>Lecture du 15/10 sur la base en ligne : 6 comptes sur 7 acceptent encore le mot de passe commun du jeu de données — cossi@, jeremie.declercq@, houefa@bigfiveabidjan.com, editeur@bigfive.ci, formateur@bigfive.ci, aya@example.ci. Seul jeanluc@ l'a changé.</t>
+          <t>Les 6 comptes qui acceptaient le mot de passe commun (cossi@, jeremie.declercq@, houefa@, editeur@, formateur@, aya@) ont été renouvelés ; contrôle en lecture seule : aucun ne l'accepte plus.</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -4801,7 +4804,7 @@
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>Mot de passe retiré du README et du TODO le 15/10. Script prêt : npm run auth:renouveler (lecture seule) puis npm run auth:renouveler -- --appliquer, qui tire un mot de passe aléatoire par compte et l'affiche une seule fois dans le terminal : le reporter dans un gestionnaire, le transmettre à son titulaire. Puis remplacer NUXT_SESSION_PASSWORD sur Vercel pour fermer les sessions ouvertes.</t>
+          <t>Transmettre chaque mot de passe à son titulaire, qui le change à sa première connexion. Remplacer NUXT_SESSION_PASSWORD sur Vercel et redéployer.</t>
         </is>
       </c>
       <c r="H25" s="50" t="inlineStr">
@@ -5105,6 +5108,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
         <is>
@@ -13374,14 +13379,14 @@
           <t>Le mot de passe n'est plus affiché sur les écrans de connexion. Il reste écrit dans le README et c'est encore celui de tous les comptes du jeu de données : à changer avant ouverture.</t>
         </is>
       </c>
-      <c r="M132" s="56" t="inlineStr">
-        <is>
-          <t>KO</t>
+      <c r="M132" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N132" s="33" t="inlineStr">
         <is>
-          <t>Le 15/10, 6 comptes sur 7 acceptent encore le mot de passe de démonstration, dont l'administrateur principal cossi@bigfiveabidjan.com (seul jeanluc@ a été changé). Retiré du README le 15/10 ; script npm run auth:renouveler prêt, à lancer par Big Five (voir « En attente client », D2).</t>
+          <t>Renouvelé le 15/10 au soir (npm run auth:renouveler -- --appliquer) : les 6 comptes concernés ont un mot de passe aléatoire de 24 caractères ; le contrôle en lecture seule confirme qu'aucun compte n'accepte plus le mot de passe de démonstration. Reste : remplacer NUXT_SESSION_PASSWORD sur Vercel et redéployer, pour fermer les sessions ouvertes.</t>
         </is>
       </c>
       <c r="O132" s="33" t="n"/>
@@ -16074,7 +16079,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F20" s="33" t="inlineStr">
@@ -16089,7 +16094,7 @@
       </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
-          <t>Script prêt : npm run auth:renouveler -- --appliquer (à lancer par Big Five)</t>
+          <t>Fait le 15/10 (6 comptes renouvelés)</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16863,7 @@
       </c>
       <c r="E40" s="40" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="F40" s="33" t="inlineStr">
@@ -16873,7 +16878,7 @@
       </c>
       <c r="H40" s="33" t="inlineStr">
         <is>
-          <t>Nouveau (15/10)</t>
+          <t>Fait le 15/10 (renouvelé)</t>
         </is>
       </c>
     </row>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -2356,7 +2356,7 @@
     <row r="48" ht="27.75" customHeight="1" s="31">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>• Après le push : exécuter les migrations 37 et 38 (déjà prévu), puis vérifier en ligne les 9 cas « À retester ».</t>
+          <t>• Migrations 37 et 38 exécutées et code en ligne depuis le 15/10 au soir : reste à vérifier en ligne les cas « À retester ».</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>Développé (2bc3bcc)</t>
+          <t>En ligne (15/10)</t>
         </is>
       </c>
       <c r="D28" s="50" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G28" s="50" t="inlineStr">
         <is>
-          <t>Vérifier après déploiement.</t>
+          <t>Vérifier après la première exécution du cron (4 h).</t>
         </is>
       </c>
       <c r="H28" s="51" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>Développé (2bc3bcc)</t>
+          <t>En ligne (15/10)</t>
         </is>
       </c>
       <c r="D29" s="50" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>Exécuter la migration 38 sur la base hébergée avant de déployer.</t>
+          <t>Migration 38 exécutée ; vérifier sur un paiement de coaching privé.</t>
         </is>
       </c>
       <c r="H29" s="50" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>Développé (2bc3bcc)</t>
+          <t>Fait (15/10)</t>
         </is>
       </c>
       <c r="D31" s="50" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G31" s="50" t="inlineStr">
         <is>
-          <t>Exécuter la migration 37 sur la base hébergée.</t>
+          <t>Migration 37 exécutée et vérifiée sur la base hébergée.</t>
         </is>
       </c>
       <c r="H31" s="50" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>Fusionné dans main</t>
+          <t>En ligne (15/10)</t>
         </is>
       </c>
       <c r="D32" s="50" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G32" s="50" t="inlineStr">
         <is>
-          <t>Déployer, puis vérifier les deux e-mails sur un vrai achat et une vraie délivrance.</t>
+          <t>Vérifier sur le prochain achat réel et la prochaine attestation.</t>
         </is>
       </c>
       <c r="H32" s="50" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="N38" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10 : relance quotidienne des commandes restées en attente (cron Vercel 04:00, /api/taches/commandes), qui relit leur statut chez FeexPay. À vérifier après déploiement.</t>
+          <t>En ligne depuis le déploiement du 15/10 au soir : la route /api/taches/commandes répond (401 sans clé) et le cron Vercel la lance chaque nuit à 4 h. À vérifier après la première exécution.</t>
         </is>
       </c>
       <c r="O38" s="33" t="n"/>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="N39" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10 (commit 5b98316, fusionné dans main) : e-mail de confirmation d'achat avec module ou séance, montant, moyen et référence, envoyé une seule fois par commande. À retester en ligne après déploiement, avec un vrai paiement.</t>
+          <t>En ligne depuis le déploiement du 15/10 au soir (5b98316) : e-mail de confirmation d'achat, envoyé une seule fois par commande. À vérifier sur le prochain achat réel.</t>
         </is>
       </c>
       <c r="O39" s="33" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="N77" s="33" t="inlineStr">
         <is>
-          <t>Le paiement d'une séance de coaching privé devient une transaction visible dans /admin/transactions et les revenus. Exige la migration 38 sur la base hébergée (pas encore exécutée au 15/10 au soir).</t>
+          <t>Migration 38 en place (module_id facultatif, vérifié le 15/10) et code en ligne : à vérifier sur le prochain paiement d'une séance de coaching privé.</t>
         </is>
       </c>
       <c r="O77" s="33" t="n"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="N86" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10 (commit 5b98316, fusionné dans main) : e-mail d'attestation avec le numéro EMBF, le lien vers l'attestation et le lien de vérification, envoyé à la première délivrance. À retester en ligne après déploiement.</t>
+          <t>En ligne depuis le déploiement du 15/10 au soir (5b98316) : e-mail d'attestation à la première délivrance. À vérifier sur la prochaine attestation délivrée.</t>
         </is>
       </c>
       <c r="O86" s="33" t="n"/>
@@ -13249,14 +13249,14 @@
           <t>Testé le 15/10 sur la base en ligne avec la clé publique : 43 tables sur 45 refusent (401). visionnages et reglages_attestation répondent 200 mais vide (RLS filtre tout) : le droit de lecture n'a pas été retiré comme ailleurs, à aligner.</t>
         </is>
       </c>
-      <c r="M130" s="55" t="inlineStr">
-        <is>
-          <t>À retester</t>
+      <c r="M130" s="52" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="N130" s="33" t="inlineStr">
         <is>
-          <t>Migration 37 écrite : RLS activé et droits retirés sur toutes les tables, y compris visionnages et reglages_attestation. À exécuter sur la base hébergée, puis revérifier avec la clé publique.</t>
+          <t>Migration 37 en place le 15/10 au soir, vérifié sur la base hébergée : RLS activé sur toutes les tables, aucun droit accordé à anon ni authenticated, privilèges par défaut fermés pour postgres.</t>
         </is>
       </c>
       <c r="O130" s="33" t="n"/>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="H35" s="33" t="inlineStr">
         <is>
-          <t>Migration 37 écrite, à exécuter sur la base hébergée</t>
+          <t>Fait le 15/10 (migration 37 exécutée et vérifiée)</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H36" s="33" t="inlineStr">
         <is>
-          <t>Développé le 15/10, migration 38 à exécuter avant déploiement</t>
+          <t>En ligne le 15/10 (migration 38 exécutée)</t>
         </is>
       </c>
     </row>
@@ -21161,7 +21161,7 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>Migrations 01 à 36 en place ; 37 (droits des clés publiques) et 38 (coaching privé dans Transactions) à exécuter dans SQL Editor avant le déploiement du 15/10 au soir</t>
+          <t>Migrations 01 à 38 en place sur la base hébergée (37 et 38 vérifiées le 15/10 au soir)</t>
         </is>
       </c>
     </row>

--- a/Recette E-Masterclass BigFive — clôture 15-10.xlsx
+++ b/Recette E-Masterclass BigFive — clôture 15-10.xlsx
@@ -2307,7 +2307,7 @@
     <row r="41" ht="27.75" customHeight="1" s="31">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>• Vidéos — 15 chapitres rattachés sur 72 dans la base en ligne ; lecture vérifiée sur le domaine définitif (Worker vidéo autorisé le 15/10).</t>
+          <t>• Vidéos — 49 chapitres sur 88 ont une vidéo dans la base en ligne au 20/10, dont les 36 chapitres des 5 modules pilotes livrés le 20/10 (720p et 1080p, sous-titres, transcription cliquable) ; lecture vérifiée.</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
     <row r="46" ht="27.75" customHeight="1" s="31">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>• Catalogue : 15 modules sur 18 en brouillon dans la base en ligne.</t>
+          <t>• Catalogue : 7 modules sur 19 publiés au 20/10, dont les 5 modules pilotes ; 11 en brouillon, 1 en préparation.</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -4320,7 +4319,7 @@
       </c>
       <c r="E11" s="50" t="inlineStr">
         <is>
-          <t>15 chapitres sur 72 ont une vidéo au 15/10.</t>
+          <t>49 chapitres sur 88 ont une vidéo au 20/10. Les 5 modules pilotes (36 chapitres) sont intégrés et publiés depuis le 20/10.</t>
         </is>
       </c>
       <c r="F11" s="50" t="inlineStr">
@@ -4362,7 +4361,7 @@
       </c>
       <c r="E12" s="50" t="inlineStr">
         <is>
-          <t>15 modules sur 18 sont en « Brouillon » : le catalogue public en montre 3.</t>
+          <t>11 modules sur 19 sont en « Brouillon » au 20/10 ; 7 sont publiés.</t>
         </is>
       </c>
       <c r="F12" s="50" t="inlineStr">
@@ -4677,8 +4676,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
         <is>
@@ -5108,8 +5105,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
         <is>
@@ -8864,7 +8859,7 @@
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
-          <t>Au 15/10, 15 chapitres ont une vidéo dans la base en ligne (2 au 02/09). Les vidéos se déposent depuis /admin/mediatheque.</t>
+          <t>Au 20/10, 49 chapitres ont une vidéo dans la base en ligne (15 au 15/10, 2 au 02/09), dont les 36 des 5 modules pilotes : flux 720p/1080p, sous-titres et transcription. Les autres vidéos se déposent depuis /admin/mediatheque.</t>
         </is>
       </c>
       <c r="M59" s="54" t="inlineStr">
@@ -8874,7 +8869,7 @@
       </c>
       <c r="N59" s="33" t="inlineStr">
         <is>
-          <t>15 chapitres sur 72 ont une vidéo dans la médiathèque au 15/10.</t>
+          <t>49 chapitres sur 88 ont une vidéo au 20/10. Modules pilotes vérifiés en lecture le 20/10 : bascule 720p/1080p, sous-titres, transcription synchronisée, mobile 375 px.</t>
         </is>
       </c>
       <c r="O59" s="53" t="inlineStr">
@@ -15642,7 +15637,7 @@
       </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
-          <t>15 chapitres rattachés au 15/10</t>
+          <t>49 chapitres rattachés au 20/10, dont les 5 modules pilotes complets</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15977,7 @@
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
-          <t>15 modules en brouillon dans la base en ligne au 15/10</t>
+          <t>11 modules en brouillon dans la base en ligne au 20/10 (7 publiés)</t>
         </is>
       </c>
     </row>
